--- a/Output/R_FACTOR.xlsx
+++ b/Output/R_FACTOR.xlsx
@@ -488,13 +488,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.03791469194313</v>
+        <v>20.83333333333334</v>
       </c>
       <c r="E2" t="n">
-        <v>20.73459715639811</v>
+        <v>19.72222222222222</v>
       </c>
       <c r="F2" t="n">
-        <v>19.90476190476191</v>
+        <v>19.77777777777778</v>
       </c>
       <c r="G2" t="n">
         <v>19.14691943127962</v>
@@ -506,10 +506,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>111.8241931843828</v>
+        <v>104.480252764613</v>
       </c>
     </row>
     <row r="3">
@@ -518,25 +518,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.5781990521327</v>
+        <v>23.21428571428572</v>
       </c>
       <c r="E3" t="n">
-        <v>17.89099526066351</v>
+        <v>18.75</v>
       </c>
       <c r="F3" t="n">
-        <v>13.80952380952381</v>
+        <v>16.78571428571428</v>
       </c>
       <c r="G3" t="n">
-        <v>19.33649289099526</v>
+        <v>18.5781990521327</v>
       </c>
       <c r="H3" t="n">
         <v>20</v>
@@ -545,10 +545,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>104.6152110133153</v>
+        <v>102.3281990521327</v>
       </c>
     </row>
     <row r="4">
@@ -557,37 +557,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.86729857819905</v>
+        <v>18.30357142857143</v>
       </c>
       <c r="E4" t="n">
-        <v>17.77251184834123</v>
+        <v>24.10714285714286</v>
       </c>
       <c r="F4" t="n">
-        <v>12.28571428571429</v>
+        <v>9.285714285714286</v>
       </c>
       <c r="G4" t="n">
-        <v>16.77725118483412</v>
+        <v>15.07109004739337</v>
       </c>
       <c r="H4" t="n">
         <v>20</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>99.70277589708869</v>
+        <v>96.76751861882194</v>
       </c>
     </row>
     <row r="5">
@@ -596,7 +596,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -605,28 +605,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.83886255924171</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>23.99289099526066</v>
+        <v>15.55555555555556</v>
       </c>
       <c r="F5" t="n">
-        <v>14.47619047619048</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>12.32227488151659</v>
+        <v>19.33649289099526</v>
       </c>
       <c r="H5" t="n">
         <v>20</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>99.63021891220943</v>
+        <v>96.55871511321747</v>
       </c>
     </row>
     <row r="6">
@@ -635,37 +635,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.88151658767772</v>
+        <v>15.17857142857143</v>
       </c>
       <c r="E6" t="n">
-        <v>23.99289099526066</v>
+        <v>20.53571428571428</v>
       </c>
       <c r="F6" t="n">
-        <v>15.80952380952381</v>
+        <v>18.57142857142857</v>
       </c>
       <c r="G6" t="n">
-        <v>7.488151658767772</v>
+        <v>17.25118483412322</v>
       </c>
       <c r="H6" t="n">
         <v>20</v>
       </c>
       <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
         <v>5</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="n">
-        <v>97.17208305122998</v>
+        <v>96.5368991198375</v>
       </c>
     </row>
     <row r="7">
@@ -674,7 +674,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -683,28 +683,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.37914691943128</v>
+        <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>23.45971563981043</v>
+        <v>23.47222222222222</v>
       </c>
       <c r="F7" t="n">
-        <v>10.47619047619048</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>17.34597156398104</v>
+        <v>7.488151658767772</v>
       </c>
       <c r="H7" t="n">
         <v>20</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>96.66102459941322</v>
+        <v>96.29370721432333</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +713,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -722,28 +722,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>22.6303317535545</v>
+        <v>14.72222222222222</v>
       </c>
       <c r="E8" t="n">
-        <v>22.1563981042654</v>
+        <v>23.47222222222222</v>
       </c>
       <c r="F8" t="n">
-        <v>4.285714285714286</v>
+        <v>14.22222222222222</v>
       </c>
       <c r="G8" t="n">
-        <v>15.35545023696683</v>
+        <v>12.32227488151659</v>
       </c>
       <c r="H8" t="n">
         <v>20</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>94.42789438050102</v>
+        <v>94.73894154818325</v>
       </c>
     </row>
     <row r="9">
@@ -752,25 +752,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.18009478672986</v>
+        <v>19.19642857142857</v>
       </c>
       <c r="E9" t="n">
-        <v>24.88151658767772</v>
+        <v>15.625</v>
       </c>
       <c r="F9" t="n">
-        <v>19.52380952380952</v>
+        <v>19.64285714285714</v>
       </c>
       <c r="G9" t="n">
-        <v>11.75355450236967</v>
+        <v>13.64928909952607</v>
       </c>
       <c r="H9" t="n">
         <v>20</v>
@@ -779,10 +779,10 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>93.33897540058676</v>
+        <v>93.11357481381178</v>
       </c>
     </row>
     <row r="10">
@@ -791,7 +791,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.81042654028436</v>
+        <v>18.05555555555555</v>
       </c>
       <c r="E10" t="n">
-        <v>21.2085308056872</v>
+        <v>22.77777777777778</v>
       </c>
       <c r="F10" t="n">
-        <v>18.28571428571428</v>
+        <v>9.777777777777777</v>
       </c>
       <c r="G10" t="n">
-        <v>16.96682464454976</v>
+        <v>17.34597156398104</v>
       </c>
       <c r="H10" t="n">
         <v>20</v>
@@ -818,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>91.27149627623561</v>
+        <v>92.95708267509215</v>
       </c>
     </row>
     <row r="11">
@@ -830,37 +830,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21.32701421800948</v>
+        <v>24.55357142857143</v>
       </c>
       <c r="E11" t="n">
-        <v>21.03080568720379</v>
+        <v>25</v>
       </c>
       <c r="F11" t="n">
-        <v>16.95238095238095</v>
+        <v>8.214285714285714</v>
       </c>
       <c r="G11" t="n">
-        <v>11.27962085308057</v>
+        <v>10.14218009478673</v>
       </c>
       <c r="H11" t="n">
         <v>20</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>90.5898217106748</v>
+        <v>92.91003723764388</v>
       </c>
     </row>
     <row r="12">
@@ -869,25 +869,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>23.22274881516588</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>22.86729857819905</v>
+        <v>7.142857142857142</v>
       </c>
       <c r="F12" t="n">
-        <v>17.71428571428572</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>5.308056872037915</v>
+        <v>14.50236966824645</v>
       </c>
       <c r="H12" t="n">
         <v>20</v>
@@ -896,10 +896,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>89.11238997968856</v>
+        <v>91.64522681110358</v>
       </c>
     </row>
     <row r="13">
@@ -908,25 +908,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19.07582938388625</v>
+        <v>23.66071428571428</v>
       </c>
       <c r="E13" t="n">
-        <v>18.95734597156398</v>
+        <v>18.30357142857143</v>
       </c>
       <c r="F13" t="n">
-        <v>11.71428571428572</v>
+        <v>4.642857142857143</v>
       </c>
       <c r="G13" t="n">
-        <v>14.31279620853081</v>
+        <v>19.90521327014218</v>
       </c>
       <c r="H13" t="n">
         <v>20</v>
@@ -938,7 +938,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>89.06025727826676</v>
+        <v>91.51235612728503</v>
       </c>
     </row>
     <row r="14">
@@ -947,7 +947,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -956,16 +956,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>20.14218009478673</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="E14" t="n">
-        <v>16.94312796208531</v>
+        <v>15.27777777777778</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>11.77777777777778</v>
       </c>
       <c r="G14" t="n">
-        <v>11.37440758293839</v>
+        <v>16.77725118483412</v>
       </c>
       <c r="H14" t="n">
         <v>20</v>
@@ -974,10 +974,10 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>88.45971563981043</v>
+        <v>91.0550289626119</v>
       </c>
     </row>
     <row r="15">
@@ -986,25 +986,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23.81516587677725</v>
+        <v>24.10714285714286</v>
       </c>
       <c r="E15" t="n">
-        <v>8.293838862559241</v>
+        <v>23.21428571428572</v>
       </c>
       <c r="F15" t="n">
-        <v>6.095238095238096</v>
+        <v>3.571428571428572</v>
       </c>
       <c r="G15" t="n">
-        <v>19.81042654028436</v>
+        <v>14.40758293838863</v>
       </c>
       <c r="H15" t="n">
         <v>20</v>
@@ -1013,10 +1013,10 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>88.01466937485895</v>
+        <v>90.30044008124577</v>
       </c>
     </row>
     <row r="16">
@@ -1025,37 +1025,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20.73459715639811</v>
+        <v>16.96428571428572</v>
       </c>
       <c r="E16" t="n">
-        <v>24.76303317535545</v>
+        <v>22.76785714285714</v>
       </c>
       <c r="F16" t="n">
-        <v>4.666666666666667</v>
+        <v>6.428571428571429</v>
       </c>
       <c r="G16" t="n">
-        <v>11.46919431279621</v>
+        <v>17.72511848341232</v>
       </c>
       <c r="H16" t="n">
         <v>20</v>
       </c>
       <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>5</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
       <c r="K16" t="n">
-        <v>86.63349131121643</v>
+        <v>88.88583276912661</v>
       </c>
     </row>
     <row r="17">
@@ -1064,37 +1064,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>22.1563981042654</v>
+        <v>21.875</v>
       </c>
       <c r="E17" t="n">
-        <v>9.360189573459715</v>
+        <v>24.55357142857143</v>
       </c>
       <c r="F17" t="n">
-        <v>9.428571428571429</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>15.54502369668247</v>
+        <v>7.014218009478673</v>
       </c>
       <c r="H17" t="n">
         <v>20</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>86.49018280297901</v>
+        <v>88.44278943805011</v>
       </c>
     </row>
     <row r="18">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1112,16 +1112,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.01895734597156</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="E18" t="n">
-        <v>20.37914691943128</v>
+        <v>25</v>
       </c>
       <c r="F18" t="n">
-        <v>14.95238095238095</v>
+        <v>18.88888888888889</v>
       </c>
       <c r="G18" t="n">
-        <v>20</v>
+        <v>11.75355450236967</v>
       </c>
       <c r="H18" t="n">
         <v>20</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>86.3504852177838</v>
+        <v>87.86466561348078</v>
       </c>
     </row>
     <row r="19">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1151,16 +1151,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>24.28909952606635</v>
+        <v>22.77777777777778</v>
       </c>
       <c r="E19" t="n">
-        <v>11.13744075829384</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="F19" t="n">
-        <v>4.380952380952381</v>
+        <v>17.11111111111111</v>
       </c>
       <c r="G19" t="n">
-        <v>15.7345971563981</v>
+        <v>5.308056872037915</v>
       </c>
       <c r="H19" t="n">
         <v>20</v>
@@ -1169,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>85.54208982171068</v>
+        <v>87.41916798314902</v>
       </c>
     </row>
     <row r="20">
@@ -1181,25 +1181,25 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IOC</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.42654028436019</v>
+        <v>22.32142857142857</v>
       </c>
       <c r="E20" t="n">
-        <v>24.17061611374407</v>
+        <v>7.8125</v>
       </c>
       <c r="F20" t="n">
-        <v>11.80952380952381</v>
+        <v>15.35714285714286</v>
       </c>
       <c r="G20" t="n">
-        <v>18.1042654028436</v>
+        <v>16.6824644549763</v>
       </c>
       <c r="H20" t="n">
         <v>20</v>
@@ -1208,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>84.51094561047168</v>
+        <v>87.17353588354773</v>
       </c>
     </row>
     <row r="21">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1229,16 +1229,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>19.90521327014218</v>
+        <v>19.72222222222222</v>
       </c>
       <c r="E21" t="n">
-        <v>12.38151658767772</v>
+        <v>20.13888888888889</v>
       </c>
       <c r="F21" t="n">
-        <v>7.428571428571429</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>19.0521327014218</v>
+        <v>11.27962085308057</v>
       </c>
       <c r="H21" t="n">
         <v>20</v>
@@ -1247,10 +1247,10 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>83.76743398781313</v>
+        <v>87.14073196419169</v>
       </c>
     </row>
     <row r="22">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>20.02369668246446</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="E22" t="n">
-        <v>22.51184834123223</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>3.333333333333333</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>12.89099526066351</v>
+        <v>15.35545023696683</v>
       </c>
       <c r="H22" t="n">
         <v>20</v>
@@ -1289,7 +1289,7 @@
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>83.75987361769353</v>
+        <v>86.35545023696682</v>
       </c>
     </row>
     <row r="23">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1307,16 +1307,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.90047393364929</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="E23" t="n">
-        <v>19.84597156398104</v>
+        <v>20.55555555555555</v>
       </c>
       <c r="F23" t="n">
-        <v>14</v>
+        <v>17.77777777777778</v>
       </c>
       <c r="G23" t="n">
-        <v>18.76777251184834</v>
+        <v>16.96682464454976</v>
       </c>
       <c r="H23" t="n">
         <v>20</v>
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>83.51421800947867</v>
+        <v>83.63349131121643</v>
       </c>
     </row>
     <row r="24">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1346,16 +1346,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.04739336492891</v>
+        <v>17.77777777777778</v>
       </c>
       <c r="E24" t="n">
-        <v>23.5781990521327</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="F24" t="n">
-        <v>10.19047619047619</v>
+        <v>20</v>
       </c>
       <c r="G24" t="n">
-        <v>14.59715639810426</v>
+        <v>11.37440758293839</v>
       </c>
       <c r="H24" t="n">
         <v>20</v>
@@ -1367,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>83.41322500564206</v>
+        <v>83.31885202738283</v>
       </c>
     </row>
     <row r="25">
@@ -1376,25 +1376,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>20.49763033175356</v>
+        <v>19.64285714285714</v>
       </c>
       <c r="E25" t="n">
-        <v>19.84597156398104</v>
+        <v>13.83928571428572</v>
       </c>
       <c r="F25" t="n">
-        <v>3.619047619047619</v>
+        <v>12.5</v>
       </c>
       <c r="G25" t="n">
-        <v>14.02843601895735</v>
+        <v>12.22748815165877</v>
       </c>
       <c r="H25" t="n">
         <v>20</v>
@@ -1406,7 +1406,7 @@
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>82.99108553373956</v>
+        <v>83.20963100880164</v>
       </c>
     </row>
     <row r="26">
@@ -1415,37 +1415,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>24.40758293838863</v>
+        <v>15.27777777777778</v>
       </c>
       <c r="E26" t="n">
-        <v>5.687203791469194</v>
+        <v>17.5</v>
       </c>
       <c r="F26" t="n">
-        <v>11.33333333333333</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G26" t="n">
-        <v>16.11374407582938</v>
+        <v>14.31279620853081</v>
       </c>
       <c r="H26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>82.54186413902053</v>
+        <v>83.2016850974197</v>
       </c>
     </row>
     <row r="27">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1463,28 +1463,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.28436018957346</v>
+        <v>18.61111111111111</v>
       </c>
       <c r="E27" t="n">
-        <v>24.5260663507109</v>
+        <v>24.72222222222222</v>
       </c>
       <c r="F27" t="n">
-        <v>16.28571428571428</v>
+        <v>3.111111111111111</v>
       </c>
       <c r="G27" t="n">
-        <v>6.445497630331753</v>
+        <v>11.46919431279621</v>
       </c>
       <c r="H27" t="n">
         <v>20</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>82.54163845633039</v>
+        <v>82.91363875724065</v>
       </c>
     </row>
     <row r="28">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1502,16 +1502,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>20.97156398104265</v>
+        <v>17.5</v>
       </c>
       <c r="E28" t="n">
-        <v>9.478672985781991</v>
+        <v>21.94444444444444</v>
       </c>
       <c r="F28" t="n">
-        <v>19.14285714285714</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>12.13270142180095</v>
+        <v>12.89099526066351</v>
       </c>
       <c r="H28" t="n">
         <v>20</v>
@@ -1520,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>81.72579553148273</v>
+        <v>79.33543970510794</v>
       </c>
     </row>
     <row r="29">
@@ -1532,25 +1532,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>9.834123222748815</v>
+        <v>17.41071428571428</v>
       </c>
       <c r="E29" t="n">
-        <v>20.49763033175356</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="F29" t="n">
-        <v>15.61904761904762</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="G29" t="n">
-        <v>15.63981042654028</v>
+        <v>16.87203791469194</v>
       </c>
       <c r="H29" t="n">
         <v>20</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>81.59061160009027</v>
+        <v>79.28275220040624</v>
       </c>
     </row>
     <row r="30">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1580,16 +1580,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>22.98578199052132</v>
+        <v>18.33333333333333</v>
       </c>
       <c r="E30" t="n">
-        <v>10.18957345971564</v>
+        <v>18.47222222222222</v>
       </c>
       <c r="F30" t="n">
-        <v>18.95238095238095</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="G30" t="n">
-        <v>9.289099526066352</v>
+        <v>14.02843601895735</v>
       </c>
       <c r="H30" t="n">
         <v>20</v>
@@ -1598,10 +1598,10 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>81.41683592868426</v>
+        <v>78.05621379673512</v>
       </c>
     </row>
     <row r="31">
@@ -1610,25 +1610,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.55924170616114</v>
+        <v>20.98214285714286</v>
       </c>
       <c r="E31" t="n">
-        <v>11.96682464454976</v>
+        <v>21.875</v>
       </c>
       <c r="F31" t="n">
-        <v>18.47619047619048</v>
+        <v>5.357142857142857</v>
       </c>
       <c r="G31" t="n">
-        <v>18.38862559241706</v>
+        <v>8.720379146919431</v>
       </c>
       <c r="H31" t="n">
         <v>20</v>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>81.39088241931843</v>
+        <v>76.93466486120515</v>
       </c>
     </row>
     <row r="32">
@@ -1649,25 +1649,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>21.44549763033175</v>
+        <v>13.39285714285714</v>
       </c>
       <c r="E32" t="n">
-        <v>12.91469194312796</v>
+        <v>20.08928571428572</v>
       </c>
       <c r="F32" t="n">
-        <v>17.33333333333334</v>
+        <v>17.85714285714286</v>
       </c>
       <c r="G32" t="n">
-        <v>9.57345971563981</v>
+        <v>5.592417061611375</v>
       </c>
       <c r="H32" t="n">
         <v>20</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>81.26698262243286</v>
+        <v>76.93170277589709</v>
       </c>
     </row>
     <row r="33">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1697,16 +1697,16 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>18.48341232227488</v>
+        <v>3.055555555555555</v>
       </c>
       <c r="E33" t="n">
-        <v>15.16587677725119</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="F33" t="n">
-        <v>8.095238095238095</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="G33" t="n">
-        <v>14.12322274881516</v>
+        <v>20</v>
       </c>
       <c r="H33" t="n">
         <v>20</v>
@@ -1715,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>80.86774994357933</v>
+        <v>76.88888888888889</v>
       </c>
     </row>
     <row r="34">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1736,16 +1736,16 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>18.60189573459716</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="E34" t="n">
-        <v>15.04739336492891</v>
+        <v>24.44444444444444</v>
       </c>
       <c r="F34" t="n">
-        <v>8.857142857142858</v>
+        <v>15.55555555555556</v>
       </c>
       <c r="G34" t="n">
-        <v>13.17535545023697</v>
+        <v>6.445497630331753</v>
       </c>
       <c r="H34" t="n">
         <v>20</v>
@@ -1754,10 +1754,10 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>80.68178740690588</v>
+        <v>75.8899420747762</v>
       </c>
     </row>
     <row r="35">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1775,16 +1775,16 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.27014218009479</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="E35" t="n">
-        <v>24.28909952606635</v>
+        <v>23.05555555555556</v>
       </c>
       <c r="F35" t="n">
-        <v>10.09523809523809</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="G35" t="n">
-        <v>12.51184834123223</v>
+        <v>14.59715639810426</v>
       </c>
       <c r="H35" t="n">
         <v>20</v>
@@ -1796,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>80.16632814263146</v>
+        <v>75.87493417588205</v>
       </c>
     </row>
     <row r="36">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1814,16 +1814,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>16.94312796208531</v>
+        <v>17.22222222222222</v>
       </c>
       <c r="E36" t="n">
-        <v>21.6824644549763</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="F36" t="n">
-        <v>14.0952380952381</v>
+        <v>6.222222222222222</v>
       </c>
       <c r="G36" t="n">
-        <v>7.393364928909953</v>
+        <v>19.0521327014218</v>
       </c>
       <c r="H36" t="n">
         <v>20</v>
@@ -1832,10 +1832,10 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>80.11419544120966</v>
+        <v>75.27435492364403</v>
       </c>
     </row>
     <row r="37">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>IOC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1853,16 +1853,16 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.15165876777251</v>
+        <v>1.944444444444444</v>
       </c>
       <c r="E37" t="n">
-        <v>21.32701421800948</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="F37" t="n">
-        <v>12</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="G37" t="n">
-        <v>13.55450236966825</v>
+        <v>18.1042654028436</v>
       </c>
       <c r="H37" t="n">
         <v>20</v>
@@ -1874,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>80.03317535545024</v>
+        <v>75.27093206951027</v>
       </c>
     </row>
     <row r="38">
@@ -1883,25 +1883,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>16.11374407582938</v>
+        <v>16.51785714285714</v>
       </c>
       <c r="E38" t="n">
-        <v>16.35071090047393</v>
+        <v>5.357142857142857</v>
       </c>
       <c r="F38" t="n">
-        <v>17.04761904761905</v>
+        <v>15</v>
       </c>
       <c r="G38" t="n">
-        <v>10.33175355450237</v>
+        <v>13.36492890995261</v>
       </c>
       <c r="H38" t="n">
         <v>20</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>79.84382757842474</v>
+        <v>75.23992890995261</v>
       </c>
     </row>
     <row r="39">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1931,16 +1931,16 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.57345971563981</v>
+        <v>22.5</v>
       </c>
       <c r="E39" t="n">
-        <v>20.14218009478673</v>
+        <v>5</v>
       </c>
       <c r="F39" t="n">
-        <v>14.85714285714286</v>
+        <v>18.44444444444445</v>
       </c>
       <c r="G39" t="n">
-        <v>9.19431279620853</v>
+        <v>9.289099526066352</v>
       </c>
       <c r="H39" t="n">
         <v>20</v>
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>78.76709546377793</v>
+        <v>75.23354397051079</v>
       </c>
     </row>
     <row r="40">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1970,16 +1970,16 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>16.23222748815166</v>
+        <v>20</v>
       </c>
       <c r="E40" t="n">
-        <v>15.63981042654028</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="F40" t="n">
-        <v>11.52380952380952</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="G40" t="n">
-        <v>15.16587677725118</v>
+        <v>9.57345971563981</v>
       </c>
       <c r="H40" t="n">
         <v>20</v>
@@ -1991,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>78.56172421575265</v>
+        <v>75.12901527119537</v>
       </c>
     </row>
     <row r="41">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2009,16 +2009,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>19.19431279620853</v>
+        <v>24.72222222222222</v>
       </c>
       <c r="E41" t="n">
-        <v>12.55924170616114</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="F41" t="n">
-        <v>8.571428571428571</v>
+        <v>2.888888888888888</v>
       </c>
       <c r="G41" t="n">
-        <v>13.08056872037915</v>
+        <v>15.7345971563981</v>
       </c>
       <c r="H41" t="n">
         <v>20</v>
@@ -2030,7 +2030,7 @@
         <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>78.40555179417738</v>
+        <v>74.45681937862032</v>
       </c>
     </row>
     <row r="42">
@@ -2039,25 +2039,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>19.7867298578199</v>
+        <v>6.696428571428571</v>
       </c>
       <c r="E42" t="n">
-        <v>8.412322274881516</v>
+        <v>19.64285714285714</v>
       </c>
       <c r="F42" t="n">
-        <v>19.80952380952381</v>
+        <v>13.21428571428571</v>
       </c>
       <c r="G42" t="n">
-        <v>10.23696682464455</v>
+        <v>14.88151658767773</v>
       </c>
       <c r="H42" t="n">
         <v>20</v>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>78.24554276686978</v>
+        <v>74.43508801624915</v>
       </c>
     </row>
     <row r="43">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.08530805687204</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="E43" t="n">
-        <v>15.75829383886256</v>
+        <v>22.5</v>
       </c>
       <c r="F43" t="n">
-        <v>13.14285714285714</v>
+        <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>17.1563981042654</v>
+        <v>1.611374407582938</v>
       </c>
       <c r="H43" t="n">
         <v>20</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>78.14285714285714</v>
+        <v>74.27804107424961</v>
       </c>
     </row>
     <row r="44">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2126,16 +2126,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>19.31279620853081</v>
+        <v>11.94444444444444</v>
       </c>
       <c r="E44" t="n">
-        <v>11.49289099526066</v>
+        <v>21.11111111111111</v>
       </c>
       <c r="F44" t="n">
-        <v>7.619047619047619</v>
+        <v>13.77777777777778</v>
       </c>
       <c r="G44" t="n">
-        <v>14.21800947867299</v>
+        <v>7.393364928909953</v>
       </c>
       <c r="H44" t="n">
         <v>20</v>
@@ -2144,10 +2144,10 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>77.64274430151207</v>
+        <v>74.22669826224329</v>
       </c>
     </row>
     <row r="45">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2165,16 +2165,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.72985781990521</v>
+        <v>23.61111111111111</v>
       </c>
       <c r="E45" t="n">
-        <v>17.35781990521327</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F45" t="n">
-        <v>8.285714285714286</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="G45" t="n">
-        <v>19.62085308056872</v>
+        <v>19.81042654028436</v>
       </c>
       <c r="H45" t="n">
         <v>20</v>
@@ -2183,10 +2183,10 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>76.9942450914015</v>
+        <v>73.92153765139547</v>
       </c>
     </row>
     <row r="46">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2204,16 +2204,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>18.12796208530806</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="E46" t="n">
-        <v>11.84834123222749</v>
+        <v>3.611111111111111</v>
       </c>
       <c r="F46" t="n">
-        <v>18</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="G46" t="n">
-        <v>8.909952606635072</v>
+        <v>12.13270142180095</v>
       </c>
       <c r="H46" t="n">
         <v>20</v>
@@ -2225,7 +2225,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>76.88625592417063</v>
+        <v>73.57714586624539</v>
       </c>
     </row>
     <row r="47">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2243,16 +2243,16 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>21.80094786729858</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="E47" t="n">
-        <v>11.01895734597156</v>
+        <v>18.47222222222222</v>
       </c>
       <c r="F47" t="n">
-        <v>19.61904761904762</v>
+        <v>13.55555555555556</v>
       </c>
       <c r="G47" t="n">
-        <v>4.360189573459715</v>
+        <v>18.76777251184834</v>
       </c>
       <c r="H47" t="n">
         <v>20</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>76.79914240577747</v>
+        <v>73.57332806740391</v>
       </c>
     </row>
     <row r="48">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NBCC</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2282,16 +2282,16 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>15.16587677725119</v>
+        <v>21.11111111111111</v>
       </c>
       <c r="E48" t="n">
-        <v>14.69194312796208</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="F48" t="n">
-        <v>8.380952380952381</v>
+        <v>8.444444444444445</v>
       </c>
       <c r="G48" t="n">
-        <v>18.00947867298578</v>
+        <v>15.54502369668247</v>
       </c>
       <c r="H48" t="n">
         <v>20</v>
@@ -2300,10 +2300,10 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>76.24825095915143</v>
+        <v>73.43391258557135</v>
       </c>
     </row>
     <row r="49">
@@ -2312,25 +2312,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>24.0521327014218</v>
+        <v>8.035714285714286</v>
       </c>
       <c r="E49" t="n">
-        <v>23.1042654028436</v>
+        <v>12.05357142857143</v>
       </c>
       <c r="F49" t="n">
-        <v>7.333333333333333</v>
+        <v>17.14285714285714</v>
       </c>
       <c r="G49" t="n">
-        <v>1.611374407582938</v>
+        <v>15.45023696682464</v>
       </c>
       <c r="H49" t="n">
         <v>20</v>
@@ -2342,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>76.10110584518168</v>
+        <v>72.68237982396751</v>
       </c>
     </row>
     <row r="50">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2360,16 +2360,16 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.18957345971564</v>
+        <v>24.44444444444444</v>
       </c>
       <c r="E50" t="n">
-        <v>15.52132701421801</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="F50" t="n">
-        <v>10.66666666666667</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="G50" t="n">
-        <v>19.5260663507109</v>
+        <v>6.635071090047393</v>
       </c>
       <c r="H50" t="n">
         <v>20</v>
@@ -2381,7 +2381,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>75.90363349131121</v>
+        <v>72.46840442338072</v>
       </c>
     </row>
     <row r="51">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2399,16 +2399,16 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.99526066350711</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="E51" t="n">
-        <v>17.53554502369668</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="F51" t="n">
-        <v>17.42857142857143</v>
+        <v>9.111111111111111</v>
       </c>
       <c r="G51" t="n">
-        <v>4.928909952606634</v>
+        <v>12.51184834123223</v>
       </c>
       <c r="H51" t="n">
         <v>20</v>
@@ -2420,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>75.88828706838186</v>
+        <v>72.45629278567667</v>
       </c>
     </row>
     <row r="52">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2438,16 +2438,16 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>24.17061611374407</v>
+        <v>6.388888888888888</v>
       </c>
       <c r="E52" t="n">
-        <v>18.00947867298578</v>
+        <v>20.83333333333334</v>
       </c>
       <c r="F52" t="n">
-        <v>6.952380952380953</v>
+        <v>11.55555555555555</v>
       </c>
       <c r="G52" t="n">
-        <v>6.635071090047393</v>
+        <v>13.55450236966825</v>
       </c>
       <c r="H52" t="n">
         <v>20</v>
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>75.76754682915819</v>
+        <v>72.33228014744603</v>
       </c>
     </row>
     <row r="53">
@@ -2468,25 +2468,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>19.54976303317536</v>
+        <v>18.75</v>
       </c>
       <c r="E53" t="n">
-        <v>16.70616113744076</v>
+        <v>22.32142857142857</v>
       </c>
       <c r="F53" t="n">
-        <v>12.95238095238095</v>
+        <v>1.428571428571428</v>
       </c>
       <c r="G53" t="n">
-        <v>6.350710900473934</v>
+        <v>9.763033175355449</v>
       </c>
       <c r="H53" t="n">
         <v>20</v>
@@ -2498,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>75.559016023471</v>
+        <v>72.26303317535545</v>
       </c>
     </row>
     <row r="54">
@@ -2507,25 +2507,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>16.58767772511848</v>
+        <v>4.017857142857143</v>
       </c>
       <c r="E54" t="n">
-        <v>15.40284360189574</v>
+        <v>14.73214285714286</v>
       </c>
       <c r="F54" t="n">
-        <v>19.71428571428572</v>
+        <v>13.57142857142857</v>
       </c>
       <c r="G54" t="n">
-        <v>3.317535545023697</v>
+        <v>19.43127962085308</v>
       </c>
       <c r="H54" t="n">
         <v>20</v>
@@ -2537,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>75.02234258632362</v>
+        <v>71.75270819228166</v>
       </c>
     </row>
     <row r="55">
@@ -2546,25 +2546,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.86255924170616</v>
+        <v>20.08928571428572</v>
       </c>
       <c r="E55" t="n">
-        <v>14.45497630331753</v>
+        <v>12.94642857142857</v>
       </c>
       <c r="F55" t="n">
-        <v>17.14285714285714</v>
+        <v>16.42857142857143</v>
       </c>
       <c r="G55" t="n">
-        <v>9.478672985781991</v>
+        <v>2.085308056872038</v>
       </c>
       <c r="H55" t="n">
         <v>20</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>74.93906567366284</v>
+        <v>71.54959377115776</v>
       </c>
     </row>
     <row r="56">
@@ -2585,25 +2585,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.66350710900474</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="E56" t="n">
-        <v>13.98104265402844</v>
+        <v>0.6696428571428571</v>
       </c>
       <c r="F56" t="n">
-        <v>14.38095238095238</v>
+        <v>19.28571428571428</v>
       </c>
       <c r="G56" t="n">
-        <v>15.82938388625592</v>
+        <v>9.857819905213269</v>
       </c>
       <c r="H56" t="n">
         <v>20</v>
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>74.85488603024149</v>
+        <v>71.24174847664185</v>
       </c>
     </row>
     <row r="57">
@@ -2624,37 +2624,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>22.39336492890995</v>
+        <v>14.44444444444444</v>
       </c>
       <c r="E57" t="n">
-        <v>5.035545023696683</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="F57" t="n">
-        <v>5.047619047619047</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G57" t="n">
-        <v>17.06161137440758</v>
+        <v>13.17535545023697</v>
       </c>
       <c r="H57" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>74.53814037463326</v>
+        <v>71.23091100579252</v>
       </c>
     </row>
     <row r="58">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2672,16 +2672,16 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>21.09004739336493</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="E58" t="n">
-        <v>10.42654028436019</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="F58" t="n">
-        <v>18.85714285714286</v>
+        <v>6.666666666666666</v>
       </c>
       <c r="G58" t="n">
-        <v>3.791469194312796</v>
+        <v>14.12322274881516</v>
       </c>
       <c r="H58" t="n">
         <v>20</v>
@@ -2690,10 +2690,10 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>74.16519972918077</v>
+        <v>71.06766719325961</v>
       </c>
     </row>
     <row r="59">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2711,16 +2711,16 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.13744075829384</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E59" t="n">
-        <v>19.54976303317536</v>
+        <v>19.44444444444445</v>
       </c>
       <c r="F59" t="n">
-        <v>18.09523809523809</v>
+        <v>15.11111111111111</v>
       </c>
       <c r="G59" t="n">
-        <v>5.118483412322274</v>
+        <v>15.63981042654028</v>
       </c>
       <c r="H59" t="n">
         <v>20</v>
@@ -2732,7 +2732,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>73.90092529902957</v>
+        <v>71.02869931542917</v>
       </c>
     </row>
     <row r="60">
@@ -2741,25 +2741,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.07109004739337</v>
+        <v>9.821428571428571</v>
       </c>
       <c r="E60" t="n">
-        <v>16.82464454976303</v>
+        <v>20.98214285714286</v>
       </c>
       <c r="F60" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="G60" t="n">
-        <v>16.58767772511848</v>
+        <v>12.60663507109005</v>
       </c>
       <c r="H60" t="n">
         <v>20</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>73.48341232227489</v>
+        <v>70.91020649966148</v>
       </c>
     </row>
     <row r="61">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2789,16 +2789,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.61137440758294</v>
+        <v>8.055555555555555</v>
       </c>
       <c r="E61" t="n">
-        <v>18.36492890995261</v>
+        <v>18.88888888888889</v>
       </c>
       <c r="F61" t="n">
-        <v>6.761904761904763</v>
+        <v>14.44444444444444</v>
       </c>
       <c r="G61" t="n">
-        <v>16.49289099526066</v>
+        <v>9.19431279620853</v>
       </c>
       <c r="H61" t="n">
         <v>20</v>
@@ -2810,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>73.23109907470098</v>
+        <v>70.58320168509741</v>
       </c>
     </row>
     <row r="62">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2828,16 +2828,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>22.74881516587678</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="E62" t="n">
-        <v>16.58767772511848</v>
+        <v>13.05555555555556</v>
       </c>
       <c r="F62" t="n">
-        <v>3.142857142857143</v>
+        <v>16.22222222222222</v>
       </c>
       <c r="G62" t="n">
-        <v>10.71090047393365</v>
+        <v>10.33175355450237</v>
       </c>
       <c r="H62" t="n">
         <v>20</v>
@@ -2849,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>73.19025050778606</v>
+        <v>70.44286466561348</v>
       </c>
     </row>
     <row r="63">
@@ -2858,25 +2858,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>18.95734597156398</v>
+        <v>9.375</v>
       </c>
       <c r="E63" t="n">
-        <v>12.79620853080569</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="F63" t="n">
-        <v>13.23809523809524</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="G63" t="n">
-        <v>7.298578199052132</v>
+        <v>16.01895734597156</v>
       </c>
       <c r="H63" t="n">
         <v>20</v>
@@ -2888,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>72.29022793951704</v>
+        <v>69.67967163168585</v>
       </c>
     </row>
     <row r="64">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2906,16 +2906,16 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>14.21800947867299</v>
+        <v>20.27777777777778</v>
       </c>
       <c r="E64" t="n">
-        <v>12.08530805687204</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="F64" t="n">
-        <v>9.333333333333334</v>
+        <v>19.11111111111111</v>
       </c>
       <c r="G64" t="n">
-        <v>15.92417061611375</v>
+        <v>4.360189573459715</v>
       </c>
       <c r="H64" t="n">
         <v>20</v>
@@ -2927,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>71.5608214849921</v>
+        <v>69.58241179568194</v>
       </c>
     </row>
     <row r="65">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2945,16 +2945,16 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>18.36492890995261</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="E65" t="n">
-        <v>18.83886255924171</v>
+        <v>7.222222222222221</v>
       </c>
       <c r="F65" t="n">
-        <v>5.714285714285714</v>
+        <v>18</v>
       </c>
       <c r="G65" t="n">
-        <v>7.962085308056873</v>
+        <v>18.38862559241706</v>
       </c>
       <c r="H65" t="n">
         <v>20</v>
@@ -2966,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>70.88016249153691</v>
+        <v>69.16640337019484</v>
       </c>
     </row>
     <row r="66">
@@ -2975,25 +2975,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>16.46919431279621</v>
+        <v>10.26785714285714</v>
       </c>
       <c r="E66" t="n">
-        <v>16.23222748815166</v>
+        <v>10.71428571428571</v>
       </c>
       <c r="F66" t="n">
-        <v>13.33333333333333</v>
+        <v>10.35714285714286</v>
       </c>
       <c r="G66" t="n">
-        <v>4.644549763033176</v>
+        <v>17.81990521327014</v>
       </c>
       <c r="H66" t="n">
         <v>20</v>
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>70.67930489731438</v>
+        <v>69.15919092755585</v>
       </c>
     </row>
     <row r="67">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UNITDSPR</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3023,16 +3023,16 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>17.89099526066351</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="E67" t="n">
-        <v>21.80094786729858</v>
+        <v>11.94444444444444</v>
       </c>
       <c r="F67" t="n">
-        <v>6</v>
+        <v>10.88888888888889</v>
       </c>
       <c r="G67" t="n">
-        <v>4.834123222748815</v>
+        <v>15.16587677725118</v>
       </c>
       <c r="H67" t="n">
         <v>20</v>
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>70.52606635071089</v>
+        <v>69.11032122169563</v>
       </c>
     </row>
     <row r="68">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3062,16 +3062,16 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>18.24644549763033</v>
+        <v>15.55555555555556</v>
       </c>
       <c r="E68" t="n">
-        <v>13.50710900473934</v>
+        <v>8.055555555555555</v>
       </c>
       <c r="F68" t="n">
-        <v>16.66666666666667</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="G68" t="n">
-        <v>1.421800947867299</v>
+        <v>13.08056872037915</v>
       </c>
       <c r="H68" t="n">
         <v>20</v>
@@ -3080,10 +3080,10 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K68" t="n">
-        <v>69.84202211690364</v>
+        <v>69.02501316482359</v>
       </c>
     </row>
     <row r="69">
@@ -3092,25 +3092,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>14.92890995260663</v>
+        <v>1.339285714285714</v>
       </c>
       <c r="E69" t="n">
-        <v>19.19431279620853</v>
+        <v>23.66071428571428</v>
       </c>
       <c r="F69" t="n">
-        <v>2.761904761904762</v>
+        <v>12.14285714285714</v>
       </c>
       <c r="G69" t="n">
-        <v>12.79620853080569</v>
+        <v>11.84834123222749</v>
       </c>
       <c r="H69" t="n">
         <v>20</v>
@@ -3122,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>69.68133604152561</v>
+        <v>68.99119837508462</v>
       </c>
     </row>
     <row r="70">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3140,16 +3140,16 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.54502369668247</v>
+        <v>16.38888888888889</v>
       </c>
       <c r="E70" t="n">
-        <v>8.767772511848342</v>
+        <v>13.61111111111111</v>
       </c>
       <c r="F70" t="n">
-        <v>15.33333333333333</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G70" t="n">
-        <v>14.97630331753554</v>
+        <v>6.350710900473934</v>
       </c>
       <c r="H70" t="n">
         <v>20</v>
@@ -3161,7 +3161,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>69.62243285939968</v>
+        <v>68.57293312269616</v>
       </c>
     </row>
     <row r="71">
@@ -3170,37 +3170,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>24.5260663507109</v>
+        <v>2.678571428571428</v>
       </c>
       <c r="E71" t="n">
-        <v>0.1184834123222749</v>
+        <v>8.482142857142858</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>18.92857142857143</v>
       </c>
       <c r="G71" t="n">
-        <v>19.71563981042654</v>
+        <v>18.19905213270142</v>
       </c>
       <c r="H71" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>69.36018957345971</v>
+        <v>68.28833784698713</v>
       </c>
     </row>
     <row r="72">
@@ -3209,25 +3209,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>AMBUJACEM</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>15.87677725118483</v>
+        <v>4.910714285714286</v>
       </c>
       <c r="E72" t="n">
-        <v>18.12796208530806</v>
+        <v>19.19642857142857</v>
       </c>
       <c r="F72" t="n">
-        <v>6.857142857142858</v>
+        <v>12.85714285714286</v>
       </c>
       <c r="G72" t="n">
-        <v>8.151658767772512</v>
+        <v>11.09004739336493</v>
       </c>
       <c r="H72" t="n">
         <v>20</v>
@@ -3239,7 +3239,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>69.01354096140827</v>
+        <v>68.05433310765065</v>
       </c>
     </row>
     <row r="73">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>17.41706161137441</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="E73" t="n">
-        <v>18.60189573459716</v>
+        <v>6.388888888888888</v>
       </c>
       <c r="F73" t="n">
-        <v>2.190476190476191</v>
+        <v>6.444444444444445</v>
       </c>
       <c r="G73" t="n">
-        <v>10.52132701421801</v>
+        <v>14.21800947867299</v>
       </c>
       <c r="H73" t="n">
         <v>20</v>
@@ -3275,10 +3275,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K73" t="n">
-        <v>68.73076055066576</v>
+        <v>67.88467614533965</v>
       </c>
     </row>
     <row r="74">
@@ -3287,37 +3287,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>21.56398104265403</v>
+        <v>16.94444444444445</v>
       </c>
       <c r="E74" t="n">
-        <v>3.436018957345972</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="F74" t="n">
-        <v>9.714285714285714</v>
+        <v>19.55555555555555</v>
       </c>
       <c r="G74" t="n">
-        <v>13.93364928909953</v>
+        <v>10.23696682464455</v>
       </c>
       <c r="H74" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>68.64793500338524</v>
+        <v>67.84807793575567</v>
       </c>
     </row>
     <row r="75">
@@ -3326,25 +3326,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>19.43127962085308</v>
+        <v>6.25</v>
       </c>
       <c r="E75" t="n">
-        <v>10.90047393364929</v>
+        <v>6.25</v>
       </c>
       <c r="F75" t="n">
-        <v>11.04761904761905</v>
+        <v>16.07142857142857</v>
       </c>
       <c r="G75" t="n">
-        <v>6.824644549763033</v>
+        <v>19.24170616113744</v>
       </c>
       <c r="H75" t="n">
         <v>20</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>68.20401715188446</v>
+        <v>67.81313473256601</v>
       </c>
     </row>
     <row r="76">
@@ -3365,37 +3365,37 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>21.2085308056872</v>
+        <v>21.94444444444444</v>
       </c>
       <c r="E76" t="n">
-        <v>2.962085308056872</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="F76" t="n">
-        <v>5.904761904761905</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="G76" t="n">
-        <v>17.6303317535545</v>
+        <v>10.71090047393365</v>
       </c>
       <c r="H76" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>67.70570977206049</v>
+        <v>67.76645602948921</v>
       </c>
     </row>
     <row r="77">
@@ -3404,28 +3404,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>17.06161137440758</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="E77" t="n">
-        <v>7.345971563981042</v>
+        <v>15</v>
       </c>
       <c r="F77" t="n">
-        <v>11.61904761904762</v>
+        <v>16.88888888888889</v>
       </c>
       <c r="G77" t="n">
-        <v>16.2085308056872</v>
+        <v>4.928909952606634</v>
       </c>
       <c r="H77" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -3434,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>67.23516136312345</v>
+        <v>67.37335439705107</v>
       </c>
     </row>
     <row r="78">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PREMIERENE</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3452,16 +3452,16 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>21.91943127962085</v>
+        <v>19.44444444444445</v>
       </c>
       <c r="E78" t="n">
-        <v>9.597156398104266</v>
+        <v>5.277777777777778</v>
       </c>
       <c r="F78" t="n">
-        <v>9.523809523809524</v>
+        <v>18.22222222222222</v>
       </c>
       <c r="G78" t="n">
-        <v>5.971563981042653</v>
+        <v>3.791469194312796</v>
       </c>
       <c r="H78" t="n">
         <v>20</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>67.01196118257729</v>
+        <v>66.73591363875724</v>
       </c>
     </row>
     <row r="79">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3491,16 +3491,16 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>23.93364928909953</v>
+        <v>4.722222222222222</v>
       </c>
       <c r="E79" t="n">
-        <v>8.649289099526067</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="F79" t="n">
-        <v>5.523809523809524</v>
+        <v>12.44444444444444</v>
       </c>
       <c r="G79" t="n">
-        <v>8.81516587677725</v>
+        <v>17.1563981042654</v>
       </c>
       <c r="H79" t="n">
         <v>20</v>
@@ -3512,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>66.92191378921237</v>
+        <v>66.54528699315429</v>
       </c>
     </row>
     <row r="80">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3530,16 +3530,16 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>23.45971563981043</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="E80" t="n">
-        <v>17.35781990521327</v>
+        <v>6.944444444444445</v>
       </c>
       <c r="F80" t="n">
-        <v>1.80952380952381</v>
+        <v>17.33333333333334</v>
       </c>
       <c r="G80" t="n">
-        <v>3.886255924170616</v>
+        <v>8.909952606635072</v>
       </c>
       <c r="H80" t="n">
         <v>20</v>
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>66.51331527871812</v>
+        <v>66.52106371774619</v>
       </c>
     </row>
     <row r="81">
@@ -3560,37 +3560,37 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>18.00947867298578</v>
+        <v>8.482142857142858</v>
       </c>
       <c r="E81" t="n">
-        <v>5.33175355450237</v>
+        <v>13.39285714285714</v>
       </c>
       <c r="F81" t="n">
-        <v>4.952380952380953</v>
+        <v>6.785714285714286</v>
       </c>
       <c r="G81" t="n">
-        <v>17.91469194312796</v>
+        <v>17.44075829383886</v>
       </c>
       <c r="H81" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>66.20830512299707</v>
+        <v>66.10147257955315</v>
       </c>
     </row>
     <row r="82">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3608,16 +3608,16 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.79620853080569</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="E82" t="n">
-        <v>14.15876777251185</v>
+        <v>11.38888888888889</v>
       </c>
       <c r="F82" t="n">
-        <v>10.76190476190476</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="G82" t="n">
-        <v>8.341232227488151</v>
+        <v>3.317535545023697</v>
       </c>
       <c r="H82" t="n">
         <v>20</v>
@@ -3629,7 +3629,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>66.05811329271044</v>
+        <v>65.70642443391259</v>
       </c>
     </row>
     <row r="83">
@@ -3638,28 +3638,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.96682464454976</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="E83" t="n">
-        <v>6.279620853080568</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="F83" t="n">
-        <v>18.66666666666667</v>
+        <v>6.888888888888889</v>
       </c>
       <c r="G83" t="n">
-        <v>13.83886255924171</v>
+        <v>19.62085308056872</v>
       </c>
       <c r="H83" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
@@ -3668,7 +3668,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>65.75197472353871</v>
+        <v>65.25974196945761</v>
       </c>
     </row>
     <row r="84">
@@ -3677,25 +3677,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.62559241706161</v>
+        <v>20.53571428571428</v>
       </c>
       <c r="E84" t="n">
-        <v>12.67772511848341</v>
+        <v>4.910714285714286</v>
       </c>
       <c r="F84" t="n">
-        <v>12.38095238095238</v>
+        <v>9.642857142857142</v>
       </c>
       <c r="G84" t="n">
-        <v>5.781990521327014</v>
+        <v>10.04739336492891</v>
       </c>
       <c r="H84" t="n">
         <v>20</v>
@@ -3707,7 +3707,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>64.46626043782442</v>
+        <v>65.13667907921462</v>
       </c>
     </row>
     <row r="85">
@@ -3716,25 +3716,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>22.27488151658768</v>
+        <v>16.07142857142857</v>
       </c>
       <c r="E85" t="n">
-        <v>14.8696682464455</v>
+        <v>0.6696428571428571</v>
       </c>
       <c r="F85" t="n">
-        <v>2.285714285714286</v>
+        <v>18.21428571428572</v>
       </c>
       <c r="G85" t="n">
-        <v>5.023696682464455</v>
+        <v>9.95260663507109</v>
       </c>
       <c r="H85" t="n">
         <v>20</v>
@@ -3746,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>64.45396073121191</v>
+        <v>64.90796377792825</v>
       </c>
     </row>
     <row r="86">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>NBCC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3764,16 +3764,16 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>9.95260663507109</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="E86" t="n">
-        <v>21.03080568720379</v>
+        <v>10.27777777777778</v>
       </c>
       <c r="F86" t="n">
-        <v>1.428571428571428</v>
+        <v>7.111111111111112</v>
       </c>
       <c r="G86" t="n">
-        <v>12.03791469194313</v>
+        <v>18.00947867298578</v>
       </c>
       <c r="H86" t="n">
         <v>20</v>
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>64.44989844278945</v>
+        <v>64.56503422854134</v>
       </c>
     </row>
     <row r="87">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3803,16 +3803,16 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.20379146919431</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="E87" t="n">
-        <v>18.72037914691943</v>
+        <v>18.05555555555555</v>
       </c>
       <c r="F87" t="n">
-        <v>7.238095238095238</v>
+        <v>17.55555555555556</v>
       </c>
       <c r="G87" t="n">
-        <v>5.497630331753554</v>
+        <v>5.118483412322274</v>
       </c>
       <c r="H87" t="n">
         <v>20</v>
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>63.65989618596254</v>
+        <v>64.06292785676672</v>
       </c>
     </row>
     <row r="88">
@@ -3833,28 +3833,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>UNITDSPR</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>14.69194312796208</v>
+        <v>13.05555555555556</v>
       </c>
       <c r="E88" t="n">
-        <v>6.161137440758294</v>
+        <v>21.38888888888889</v>
       </c>
       <c r="F88" t="n">
-        <v>7.904761904761904</v>
+        <v>4.444444444444445</v>
       </c>
       <c r="G88" t="n">
-        <v>18.67298578199052</v>
+        <v>4.834123222748815</v>
       </c>
       <c r="H88" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>62.4308282554728</v>
+        <v>63.7230121116377</v>
       </c>
     </row>
     <row r="89">
@@ -3872,28 +3872,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PAGEIND</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>23.1042654028436</v>
+        <v>5.803571428571429</v>
       </c>
       <c r="E89" t="n">
-        <v>4.028436018957346</v>
+        <v>16.51785714285714</v>
       </c>
       <c r="F89" t="n">
-        <v>19.33333333333333</v>
+        <v>6.071428571428571</v>
       </c>
       <c r="G89" t="n">
-        <v>0.2843601895734597</v>
+        <v>15.260663507109</v>
       </c>
       <c r="H89" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>61.75039494470774</v>
+        <v>63.65352064996614</v>
       </c>
     </row>
     <row r="90">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3920,16 +3920,16 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.32227488151659</v>
+        <v>15</v>
       </c>
       <c r="E90" t="n">
-        <v>15.99526066350711</v>
+        <v>8.611111111111111</v>
       </c>
       <c r="F90" t="n">
-        <v>8.666666666666668</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="G90" t="n">
-        <v>4.739336492890995</v>
+        <v>7.298578199052132</v>
       </c>
       <c r="H90" t="n">
         <v>20</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>61.72353870458136</v>
+        <v>63.57635597682991</v>
       </c>
     </row>
     <row r="91">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3959,16 +3959,16 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.84834123222749</v>
+        <v>7.5</v>
       </c>
       <c r="E91" t="n">
-        <v>9.834123222748815</v>
+        <v>10</v>
       </c>
       <c r="F91" t="n">
-        <v>6.476190476190476</v>
+        <v>16.44444444444444</v>
       </c>
       <c r="G91" t="n">
-        <v>13.45971563981043</v>
+        <v>9.478672985781991</v>
       </c>
       <c r="H91" t="n">
         <v>20</v>
@@ -3980,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>61.61837057097721</v>
+        <v>63.42311743022643</v>
       </c>
     </row>
     <row r="92">
@@ -3989,28 +3989,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.78199052132701</v>
+        <v>13.88888888888889</v>
       </c>
       <c r="E92" t="n">
-        <v>5.035545023696683</v>
+        <v>17.22222222222222</v>
       </c>
       <c r="F92" t="n">
-        <v>12.19047619047619</v>
+        <v>4.222222222222222</v>
       </c>
       <c r="G92" t="n">
-        <v>18.29383886255924</v>
+        <v>7.962085308056873</v>
       </c>
       <c r="H92" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>61.30185059805913</v>
+        <v>63.29541864139021</v>
       </c>
     </row>
     <row r="93">
@@ -4028,28 +4028,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>20.61611374407583</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="E93" t="n">
-        <v>0.3554502369668247</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="F93" t="n">
-        <v>16.76190476190476</v>
+        <v>10</v>
       </c>
       <c r="G93" t="n">
-        <v>7.772511848341233</v>
+        <v>19.5260663507109</v>
       </c>
       <c r="H93" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>60.50598059128865</v>
+        <v>62.85939968404423</v>
       </c>
     </row>
     <row r="94">
@@ -4067,25 +4067,25 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SONACOMS</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>9.715639810426541</v>
+        <v>5.357142857142857</v>
       </c>
       <c r="E94" t="n">
-        <v>11.61137440758294</v>
+        <v>16.07142857142857</v>
       </c>
       <c r="F94" t="n">
-        <v>9.238095238095239</v>
+        <v>11.42857142857143</v>
       </c>
       <c r="G94" t="n">
-        <v>9.099526066350711</v>
+        <v>9.66824644549763</v>
       </c>
       <c r="H94" t="n">
         <v>20</v>
@@ -4097,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>59.66463552245543</v>
+        <v>62.52538930264049</v>
       </c>
     </row>
     <row r="95">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KFINTECH</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4115,16 +4115,16 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>19.66824644549763</v>
+        <v>23.05555555555556</v>
       </c>
       <c r="E95" t="n">
-        <v>8.116113744075831</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="F95" t="n">
-        <v>5.333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G95" t="n">
-        <v>6.255924170616113</v>
+        <v>3.886255924170616</v>
       </c>
       <c r="H95" t="n">
         <v>20</v>
@@ -4136,7 +4136,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>59.37361769352291</v>
+        <v>62.19181147972618</v>
       </c>
     </row>
     <row r="96">
@@ -4145,28 +4145,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.44075829383886</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="E96" t="n">
-        <v>4.502369668246446</v>
+        <v>16.38888888888889</v>
       </c>
       <c r="F96" t="n">
-        <v>16.47619047619047</v>
+        <v>5.111111111111111</v>
       </c>
       <c r="G96" t="n">
-        <v>10.42654028436019</v>
+        <v>16.49289099526066</v>
       </c>
       <c r="H96" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>58.84585872263597</v>
+        <v>61.88177988414955</v>
       </c>
     </row>
     <row r="97">
@@ -4184,37 +4184,37 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IREDA</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>17.77251184834123</v>
+        <v>2.5</v>
       </c>
       <c r="E97" t="n">
-        <v>4.324644549763033</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="F97" t="n">
-        <v>1.238095238095238</v>
+        <v>14</v>
       </c>
       <c r="G97" t="n">
-        <v>14.69194312796209</v>
+        <v>15.82938388625592</v>
       </c>
       <c r="H97" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>58.02719476416159</v>
+        <v>61.77382833070037</v>
       </c>
     </row>
     <row r="98">
@@ -4223,28 +4223,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>16.70616113744076</v>
+        <v>11.38888888888889</v>
       </c>
       <c r="E98" t="n">
-        <v>6.69431279620853</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="F98" t="n">
-        <v>15.42857142857143</v>
+        <v>12.88888888888889</v>
       </c>
       <c r="G98" t="n">
-        <v>4.170616113744075</v>
+        <v>4.644549763033176</v>
       </c>
       <c r="H98" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>57.99966147596479</v>
+        <v>61.70010531858873</v>
       </c>
     </row>
     <row r="99">
@@ -4262,28 +4262,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>DABUR</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>14.09952606635071</v>
+        <v>14.73214285714286</v>
       </c>
       <c r="E99" t="n">
-        <v>7.109004739336493</v>
+        <v>17.85714285714286</v>
       </c>
       <c r="F99" t="n">
-        <v>15.04761904761905</v>
+        <v>0.3571428571428571</v>
       </c>
       <c r="G99" t="n">
-        <v>6.161137440758294</v>
+        <v>8.530805687203792</v>
       </c>
       <c r="H99" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -4292,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>57.41728729406455</v>
+        <v>61.47723425863236</v>
       </c>
     </row>
     <row r="100">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4310,28 +4310,28 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>6.872037914691943</v>
+        <v>12.05357142857143</v>
       </c>
       <c r="E100" t="n">
-        <v>22.74881516587678</v>
+        <v>17.41071428571428</v>
       </c>
       <c r="F100" t="n">
-        <v>16.57142857142857</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="G100" t="n">
-        <v>16.01895734597156</v>
+        <v>10.61611374407583</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>57.21123899796886</v>
+        <v>61.15182802979012</v>
       </c>
     </row>
     <row r="101">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4349,16 +4349,16 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>15.75829383886256</v>
+        <v>1.388888888888889</v>
       </c>
       <c r="E101" t="n">
-        <v>8.886255924170616</v>
+        <v>13.88888888888889</v>
       </c>
       <c r="F101" t="n">
-        <v>10.28571428571428</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G101" t="n">
-        <v>2.274881516587678</v>
+        <v>16.58767772511848</v>
       </c>
       <c r="H101" t="n">
         <v>20</v>
@@ -4370,7 +4370,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>57.20514556533514</v>
+        <v>60.75434439178515</v>
       </c>
     </row>
     <row r="102">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -4388,16 +4388,16 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.91469194312796</v>
+        <v>8.611111111111111</v>
       </c>
       <c r="E102" t="n">
-        <v>10.07109004739337</v>
+        <v>17.77777777777778</v>
       </c>
       <c r="F102" t="n">
-        <v>13.52380952380953</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="G102" t="n">
-        <v>0.3791469194312796</v>
+        <v>12.79620853080569</v>
       </c>
       <c r="H102" t="n">
         <v>20</v>
@@ -4409,7 +4409,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>56.88873843376213</v>
+        <v>60.74065297525013</v>
       </c>
     </row>
     <row r="103">
@@ -4418,28 +4418,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>14.45497630331753</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="n">
-        <v>7.464454976303317</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="F103" t="n">
-        <v>14.19047619047619</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="G103" t="n">
-        <v>5.687203791469194</v>
+        <v>10.52132701421801</v>
       </c>
       <c r="H103" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
@@ -4448,7 +4448,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>56.79711126156624</v>
+        <v>60.57688256977356</v>
       </c>
     </row>
     <row r="104">
@@ -4457,28 +4457,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>17.65402843601896</v>
+        <v>8.928571428571429</v>
       </c>
       <c r="E104" t="n">
-        <v>6.872037914691943</v>
+        <v>9.375</v>
       </c>
       <c r="F104" t="n">
-        <v>6.190476190476191</v>
+        <v>14.28571428571429</v>
       </c>
       <c r="G104" t="n">
-        <v>10.80568720379147</v>
+        <v>7.867298578199052</v>
       </c>
       <c r="H104" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>56.52222974497856</v>
+        <v>60.45658429248477</v>
       </c>
     </row>
     <row r="105">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4505,16 +4505,16 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>20.85308056872038</v>
+        <v>13.61111111111111</v>
       </c>
       <c r="E105" t="n">
-        <v>9.24170616113744</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="F105" t="n">
-        <v>5.428571428571428</v>
+        <v>15.77777777777778</v>
       </c>
       <c r="G105" t="n">
-        <v>0.7582938388625593</v>
+        <v>1.421800947867299</v>
       </c>
       <c r="H105" t="n">
         <v>20</v>
@@ -4526,7 +4526,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>56.2816519972918</v>
+        <v>59.97735650342285</v>
       </c>
     </row>
     <row r="106">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4544,16 +4544,16 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>13.38862559241706</v>
+        <v>10.27777777777778</v>
       </c>
       <c r="E106" t="n">
-        <v>9.95260663507109</v>
+        <v>16.11111111111111</v>
       </c>
       <c r="F106" t="n">
-        <v>1.619047619047619</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="G106" t="n">
-        <v>11.18483412322275</v>
+        <v>8.151658767772512</v>
       </c>
       <c r="H106" t="n">
         <v>20</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>56.14511396975852</v>
+        <v>59.87388098999473</v>
       </c>
     </row>
     <row r="107">
@@ -4574,28 +4574,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>18.72037914691943</v>
+        <v>2.232142857142857</v>
       </c>
       <c r="E107" t="n">
-        <v>5.80568720379147</v>
+        <v>12.5</v>
       </c>
       <c r="F107" t="n">
-        <v>3.809523809523809</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="G107" t="n">
-        <v>11.56398104265403</v>
+        <v>16.39810426540284</v>
       </c>
       <c r="H107" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
@@ -4604,7 +4604,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>54.89957120288874</v>
+        <v>59.70167569397427</v>
       </c>
     </row>
     <row r="108">
@@ -4613,28 +4613,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>16.35071090047393</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="E108" t="n">
-        <v>5.983412322274882</v>
+        <v>7.5</v>
       </c>
       <c r="F108" t="n">
-        <v>16.38095238095238</v>
+        <v>8.222222222222221</v>
       </c>
       <c r="G108" t="n">
-        <v>0.09478672985781991</v>
+        <v>15.92417061611375</v>
       </c>
       <c r="H108" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
@@ -4643,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>53.80986233355902</v>
+        <v>59.42417061611374</v>
       </c>
     </row>
     <row r="109">
@@ -4652,28 +4652,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>23.69668246445498</v>
+        <v>13.83928571428572</v>
       </c>
       <c r="E109" t="n">
-        <v>3.317535545023697</v>
+        <v>6.696428571428571</v>
       </c>
       <c r="F109" t="n">
-        <v>7.809523809523809</v>
+        <v>7.857142857142857</v>
       </c>
       <c r="G109" t="n">
-        <v>3.981042654028436</v>
+        <v>10.90047393364929</v>
       </c>
       <c r="H109" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
@@ -4682,7 +4682,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>53.80478447303092</v>
+        <v>59.29333107650643</v>
       </c>
     </row>
     <row r="110">
@@ -4691,28 +4691,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>COCHINSHIP</t>
+          <t>PREMIERENE</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>25</v>
+        <v>20.55555555555555</v>
       </c>
       <c r="E110" t="n">
-        <v>1.540284360189573</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="F110" t="n">
-        <v>1.047619047619048</v>
+        <v>8.666666666666668</v>
       </c>
       <c r="G110" t="n">
-        <v>10.99526066350711</v>
+        <v>5.971563981042653</v>
       </c>
       <c r="H110" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
@@ -4721,7 +4721,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>53.58316407131573</v>
+        <v>59.08267509215376</v>
       </c>
     </row>
     <row r="111">
@@ -4730,37 +4730,37 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>3.791469194312796</v>
+        <v>16.11111111111111</v>
       </c>
       <c r="E111" t="n">
-        <v>23.34123222748815</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="F111" t="n">
-        <v>13.71428571428572</v>
+        <v>10.44444444444444</v>
       </c>
       <c r="G111" t="n">
-        <v>17.72511848341232</v>
+        <v>6.824644549763033</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>53.57210561949899</v>
+        <v>58.93575566087414</v>
       </c>
     </row>
     <row r="112">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4778,16 +4778,16 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>17.53554502369668</v>
+        <v>23.88888888888889</v>
       </c>
       <c r="E112" t="n">
-        <v>9.123222748815166</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="F112" t="n">
-        <v>2.571428571428571</v>
+        <v>4</v>
       </c>
       <c r="G112" t="n">
-        <v>4.265402843601896</v>
+        <v>8.81516587677725</v>
       </c>
       <c r="H112" t="n">
         <v>20</v>
@@ -4799,7 +4799,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>53.49559918754232</v>
+        <v>58.37072143233281</v>
       </c>
     </row>
     <row r="113">
@@ -4808,28 +4808,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>13.50710900473934</v>
+        <v>21.38888888888889</v>
       </c>
       <c r="E113" t="n">
-        <v>1.895734597156398</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="F113" t="n">
-        <v>9.619047619047619</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="G113" t="n">
-        <v>12.98578199052133</v>
+        <v>5.023696682464455</v>
       </c>
       <c r="H113" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>53.00767321146468</v>
+        <v>58.07925223802001</v>
       </c>
     </row>
     <row r="114">
@@ -4847,25 +4847,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>9.597156398104266</v>
+        <v>15.625</v>
       </c>
       <c r="E114" t="n">
-        <v>9.004739336492891</v>
+        <v>3.125</v>
       </c>
       <c r="F114" t="n">
-        <v>11.42857142857143</v>
+        <v>10.71428571428571</v>
       </c>
       <c r="G114" t="n">
-        <v>2.748815165876777</v>
+        <v>8.056872037914692</v>
       </c>
       <c r="H114" t="n">
         <v>20</v>
@@ -4877,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>52.77928232904536</v>
+        <v>57.52115775220041</v>
       </c>
     </row>
     <row r="115">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4895,28 +4895,28 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.7109004739336493</v>
+        <v>22.76785714285714</v>
       </c>
       <c r="E115" t="n">
-        <v>21.44549763033175</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="F115" t="n">
-        <v>15.71428571428571</v>
+        <v>0.7142857142857142</v>
       </c>
       <c r="G115" t="n">
-        <v>19.90521327014218</v>
+        <v>11.94312796208531</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>52.7758970886933</v>
+        <v>57.21098510494245</v>
       </c>
     </row>
     <row r="116">
@@ -4925,28 +4925,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.30805687203791</v>
+        <v>11.16071428571429</v>
       </c>
       <c r="E116" t="n">
-        <v>5.509478672985782</v>
+        <v>5.803571428571429</v>
       </c>
       <c r="F116" t="n">
-        <v>19.23809523809524</v>
+        <v>3.928571428571428</v>
       </c>
       <c r="G116" t="n">
-        <v>2.654028436018958</v>
+        <v>16.30331753554502</v>
       </c>
       <c r="H116" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>52.70965921913789</v>
+        <v>57.19617467840217</v>
       </c>
     </row>
     <row r="117">
@@ -4964,28 +4964,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>23.34123222748815</v>
+        <v>12.94642857142857</v>
       </c>
       <c r="E117" t="n">
-        <v>6.398104265402843</v>
+        <v>3.571428571428571</v>
       </c>
       <c r="F117" t="n">
-        <v>4.476190476190476</v>
+        <v>11.78571428571429</v>
       </c>
       <c r="G117" t="n">
-        <v>3.412322274881517</v>
+        <v>8.246445497630331</v>
       </c>
       <c r="H117" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>52.62784924396299</v>
+        <v>56.55001692620176</v>
       </c>
     </row>
     <row r="118">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5012,28 +5012,28 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>7.938388625592417</v>
+        <v>4.464285714285714</v>
       </c>
       <c r="E118" t="n">
-        <v>20.02369668246446</v>
+        <v>11.60714285714286</v>
       </c>
       <c r="F118" t="n">
-        <v>13.90476190476191</v>
+        <v>13.92857142857143</v>
       </c>
       <c r="G118" t="n">
-        <v>15.260663507109</v>
+        <v>6.066350710900474</v>
       </c>
       <c r="H118" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>52.12751071992778</v>
+        <v>56.06635071090047</v>
       </c>
     </row>
     <row r="119">
@@ -5042,25 +5042,25 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Long Build-up</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>15.40284360189574</v>
+        <v>12.5</v>
       </c>
       <c r="E119" t="n">
-        <v>8.116113744075831</v>
+        <v>2.232142857142857</v>
       </c>
       <c r="F119" t="n">
-        <v>5.142857142857142</v>
+        <v>17.5</v>
       </c>
       <c r="G119" t="n">
-        <v>3.127962085308057</v>
+        <v>3.507109004739337</v>
       </c>
       <c r="H119" t="n">
         <v>20</v>
@@ -5072,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>51.78977657413677</v>
+        <v>55.7392518618822</v>
       </c>
     </row>
     <row r="120">
@@ -5081,28 +5081,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>24.76303317535545</v>
+        <v>3.571428571428571</v>
       </c>
       <c r="E120" t="n">
-        <v>2.369668246445498</v>
+        <v>9.821428571428571</v>
       </c>
       <c r="F120" t="n">
-        <v>8.19047619047619</v>
+        <v>15.71428571428571</v>
       </c>
       <c r="G120" t="n">
-        <v>1.137440758293839</v>
+        <v>6.540284360189573</v>
       </c>
       <c r="H120" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>51.46061837057098</v>
+        <v>55.64742721733243</v>
       </c>
     </row>
     <row r="121">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>GODREJCP</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5129,28 +5129,28 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>7.109004739336493</v>
+        <v>10.71428571428571</v>
       </c>
       <c r="E121" t="n">
-        <v>17.65402843601896</v>
+        <v>16.96428571428572</v>
       </c>
       <c r="F121" t="n">
-        <v>13.61904761904762</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="G121" t="n">
-        <v>17.44075829383886</v>
+        <v>5.402843601895735</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>50.82283908824193</v>
+        <v>54.86712931618145</v>
       </c>
     </row>
     <row r="122">
@@ -5159,37 +5159,37 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>5.687203791469194</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="E122" t="n">
-        <v>20.61611374407583</v>
+        <v>9.722222222222223</v>
       </c>
       <c r="F122" t="n">
-        <v>18.57142857142857</v>
+        <v>10.22222222222222</v>
       </c>
       <c r="G122" t="n">
-        <v>10.61611374407583</v>
+        <v>8.341232227488151</v>
       </c>
       <c r="H122" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>50.49085985104943</v>
+        <v>54.11901000526593</v>
       </c>
     </row>
     <row r="123">
@@ -5198,28 +5198,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>20.260663507109</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="E123" t="n">
-        <v>0.8293838862559242</v>
+        <v>1.944444444444444</v>
       </c>
       <c r="F123" t="n">
-        <v>10.38095238095238</v>
+        <v>14.88888888888889</v>
       </c>
       <c r="G123" t="n">
-        <v>3.601895734597156</v>
+        <v>14.97630331753554</v>
       </c>
       <c r="H123" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>50.07289550891447</v>
+        <v>54.0318588730911</v>
       </c>
     </row>
     <row r="124">
@@ -5237,37 +5237,37 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>6.753554502369669</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="E124" t="n">
-        <v>22.6303317535545</v>
+        <v>20.13888888888889</v>
       </c>
       <c r="F124" t="n">
-        <v>13.04761904761905</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="G124" t="n">
-        <v>12.60663507109005</v>
+        <v>12.03791469194313</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>50.03814037463327</v>
+        <v>53.51013691416535</v>
       </c>
     </row>
     <row r="125">
@@ -5276,37 +5276,37 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>8.886255924170616</v>
+        <v>7.222222222222221</v>
       </c>
       <c r="E125" t="n">
-        <v>17.06161137440758</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="F125" t="n">
-        <v>12.57142857142857</v>
+        <v>12</v>
       </c>
       <c r="G125" t="n">
-        <v>16.39810426540284</v>
+        <v>5.781990521327014</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>49.91740013540961</v>
+        <v>53.33754607688257</v>
       </c>
     </row>
     <row r="126">
@@ -5315,37 +5315,37 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.5924170616113744</v>
+        <v>5</v>
       </c>
       <c r="E126" t="n">
-        <v>23.69668246445498</v>
+        <v>16.94444444444445</v>
       </c>
       <c r="F126" t="n">
-        <v>16.09523809523809</v>
+        <v>5.777777777777777</v>
       </c>
       <c r="G126" t="n">
-        <v>14.40758293838863</v>
+        <v>5.497630331753554</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>49.79192055969307</v>
+        <v>53.21985255397578</v>
       </c>
     </row>
     <row r="127">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5363,28 +5363,28 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>2.843601895734597</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="E127" t="n">
-        <v>23.22274881516588</v>
+        <v>10.26785714285714</v>
       </c>
       <c r="F127" t="n">
-        <v>18.38095238095238</v>
+        <v>5</v>
       </c>
       <c r="G127" t="n">
-        <v>9.763033175355449</v>
+        <v>3.222748815165877</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>49.21033626720831</v>
+        <v>52.7763202437373</v>
       </c>
     </row>
     <row r="128">
@@ -5393,37 +5393,37 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>3.672985781990521</v>
+        <v>5.277777777777778</v>
       </c>
       <c r="E128" t="n">
-        <v>18.48341232227488</v>
+        <v>12.5</v>
       </c>
       <c r="F128" t="n">
-        <v>14.76190476190476</v>
+        <v>7.555555555555555</v>
       </c>
       <c r="G128" t="n">
-        <v>16.87203791469194</v>
+        <v>4.739336492890995</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>48.79034078086211</v>
+        <v>50.07266982622433</v>
       </c>
     </row>
     <row r="129">
@@ -5432,28 +5432,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>15.63981042654028</v>
+        <v>7.142857142857142</v>
       </c>
       <c r="E129" t="n">
-        <v>1.658767772511848</v>
+        <v>1.339285714285714</v>
       </c>
       <c r="F129" t="n">
-        <v>14.28571428571429</v>
+        <v>14.64285714285714</v>
       </c>
       <c r="G129" t="n">
-        <v>2.180094786729858</v>
+        <v>5.876777251184834</v>
       </c>
       <c r="H129" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>48.76438727149628</v>
+        <v>49.00177725118483</v>
       </c>
     </row>
     <row r="130">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5480,28 +5480,28 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>8.412322274881516</v>
+        <v>7.589285714285714</v>
       </c>
       <c r="E130" t="n">
-        <v>19.07582938388625</v>
+        <v>15.17857142857143</v>
       </c>
       <c r="F130" t="n">
-        <v>6.285714285714286</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="G130" t="n">
-        <v>19.43127962085308</v>
+        <v>1.516587677725119</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>48.20514556533514</v>
+        <v>48.57015910629654</v>
       </c>
     </row>
     <row r="131">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5519,28 +5519,28 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>4.383886255924171</v>
+        <v>0.8928571428571428</v>
       </c>
       <c r="E131" t="n">
-        <v>20.85308056872038</v>
+        <v>11.16071428571429</v>
       </c>
       <c r="F131" t="n">
-        <v>19.42857142857143</v>
+        <v>7.142857142857143</v>
       </c>
       <c r="G131" t="n">
-        <v>8.530805687203792</v>
+        <v>9.004739336492891</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>48.19634394041977</v>
+        <v>48.20116790792147</v>
       </c>
     </row>
     <row r="132">
@@ -5549,28 +5549,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>14.33649289099526</v>
+        <v>3.125</v>
       </c>
       <c r="E132" t="n">
-        <v>5.213270142180095</v>
+        <v>8.928571428571429</v>
       </c>
       <c r="F132" t="n">
-        <v>11.23809523809524</v>
+        <v>3.214285714285714</v>
       </c>
       <c r="G132" t="n">
-        <v>1.990521327014218</v>
+        <v>12.70142180094787</v>
       </c>
       <c r="H132" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
@@ -5579,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>47.77837959828481</v>
+        <v>47.96927894380501</v>
       </c>
     </row>
     <row r="133">
@@ -5588,28 +5588,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>13.98104265402844</v>
+        <v>4.444444444444445</v>
       </c>
       <c r="E133" t="n">
-        <v>2.132701421800948</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="F133" t="n">
-        <v>8.952380952380953</v>
+        <v>4.888888888888888</v>
       </c>
       <c r="G133" t="n">
-        <v>7.582938388625592</v>
+        <v>13.45971563981043</v>
       </c>
       <c r="H133" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>47.64906341683593</v>
+        <v>46.95971563981043</v>
       </c>
     </row>
     <row r="134">
@@ -5627,28 +5627,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>17.29857819905213</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="E134" t="n">
-        <v>1.421800947867299</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F134" t="n">
-        <v>10.95238095238095</v>
+        <v>3.555555555555556</v>
       </c>
       <c r="G134" t="n">
-        <v>2.938388625592417</v>
+        <v>6.255924170616113</v>
       </c>
       <c r="H134" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
@@ -5657,7 +5657,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>47.6111487248928</v>
+        <v>46.894813059505</v>
       </c>
     </row>
     <row r="135">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5675,28 +5675,28 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>8.649289099526067</v>
+        <v>11.60714285714286</v>
       </c>
       <c r="E135" t="n">
-        <v>14.15876777251185</v>
+        <v>4.464285714285714</v>
       </c>
       <c r="F135" t="n">
-        <v>16.19047619047619</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="G135" t="n">
-        <v>12.70142180094787</v>
+        <v>8.625592417061611</v>
       </c>
       <c r="H135" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>46.69995486346198</v>
+        <v>46.83987813134733</v>
       </c>
     </row>
     <row r="136">
@@ -5705,37 +5705,37 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>AMBER</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>6.279620853080568</v>
+        <v>18.88888888888889</v>
       </c>
       <c r="E136" t="n">
-        <v>13.03317535545024</v>
+        <v>3.055555555555555</v>
       </c>
       <c r="F136" t="n">
-        <v>16</v>
+        <v>3.777777777777778</v>
       </c>
       <c r="G136" t="n">
-        <v>16.30331753554502</v>
+        <v>0.7582938388625593</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I136" t="n">
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>46.61611374407583</v>
+        <v>46.48051606108478</v>
       </c>
     </row>
     <row r="137">
@@ -5744,28 +5744,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>22.51184834123223</v>
+        <v>17.85714285714286</v>
       </c>
       <c r="E137" t="n">
-        <v>1.066350710900474</v>
+        <v>4.017857142857143</v>
       </c>
       <c r="F137" t="n">
-        <v>0.8571428571428572</v>
+        <v>2.5</v>
       </c>
       <c r="G137" t="n">
-        <v>6.729857819905213</v>
+        <v>1.706161137440758</v>
       </c>
       <c r="H137" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
@@ -5774,7 +5774,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>46.16519972918077</v>
+        <v>46.08116113744076</v>
       </c>
     </row>
     <row r="138">
@@ -5783,37 +5783,37 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>7.582938388625593</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="E138" t="n">
-        <v>22.03791469194313</v>
+        <v>4.722222222222222</v>
       </c>
       <c r="F138" t="n">
-        <v>6.571428571428571</v>
+        <v>13.11111111111111</v>
       </c>
       <c r="G138" t="n">
-        <v>14.88151658767773</v>
+        <v>0.3791469194312796</v>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I138" t="n">
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>46.07379823967501</v>
+        <v>44.32359136387572</v>
       </c>
     </row>
     <row r="139">
@@ -5822,28 +5822,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>12.67772511848341</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="E139" t="n">
-        <v>1.303317535545024</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="F139" t="n">
-        <v>16.85714285714286</v>
+        <v>8</v>
       </c>
       <c r="G139" t="n">
-        <v>0.1895734597156398</v>
+        <v>9.099526066350711</v>
       </c>
       <c r="H139" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>46.02775897088694</v>
+        <v>44.32174828857293</v>
       </c>
     </row>
     <row r="140">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5870,16 +5870,16 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.49289099526066</v>
+        <v>10</v>
       </c>
       <c r="E140" t="n">
-        <v>8.530805687203792</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="F140" t="n">
-        <v>4</v>
+        <v>9.555555555555555</v>
       </c>
       <c r="G140" t="n">
-        <v>1.895734597156398</v>
+        <v>2.274881516587678</v>
       </c>
       <c r="H140" t="n">
         <v>20</v>
@@ -5891,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>45.91943127962085</v>
+        <v>44.05265929436545</v>
       </c>
     </row>
     <row r="141">
@@ -5900,28 +5900,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>9.478672985781991</v>
+        <v>6.944444444444445</v>
       </c>
       <c r="E141" t="n">
-        <v>2.606635071090047</v>
+        <v>4.444444444444445</v>
       </c>
       <c r="F141" t="n">
-        <v>17.52380952380953</v>
+        <v>0.4444444444444445</v>
       </c>
       <c r="G141" t="n">
-        <v>1.232227488151659</v>
+        <v>11.18483412322275</v>
       </c>
       <c r="H141" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>45.84134506883322</v>
+        <v>43.01816745655609</v>
       </c>
     </row>
     <row r="142">
@@ -5939,28 +5939,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>FORCEMOT</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>24.64454976303318</v>
+        <v>12.77777777777778</v>
       </c>
       <c r="E142" t="n">
-        <v>0.5924170616113744</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="F142" t="n">
-        <v>4.761904761904762</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="G142" t="n">
-        <v>0.5687203791469194</v>
+        <v>4.265402843601896</v>
       </c>
       <c r="H142" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I142" t="n">
         <v>0</v>
@@ -5969,7 +5969,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>45.56759196569624</v>
+        <v>41.15429173249078</v>
       </c>
     </row>
     <row r="143">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>GODREJCP</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5987,28 +5987,28 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>6.516587677725119</v>
+        <v>1.785714285714286</v>
       </c>
       <c r="E143" t="n">
-        <v>20.260663507109</v>
+        <v>2.678571428571428</v>
       </c>
       <c r="F143" t="n">
-        <v>18.19047619047619</v>
+        <v>11.07142857142857</v>
       </c>
       <c r="G143" t="n">
-        <v>5.402843601895735</v>
+        <v>2.464454976303317</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>45.37057097720605</v>
+        <v>38.00016926201761</v>
       </c>
     </row>
     <row r="144">
@@ -6017,28 +6017,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Short Build-up</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>15.52132701421801</v>
+        <v>0.4464285714285714</v>
       </c>
       <c r="E144" t="n">
-        <v>0.4739336492890995</v>
+        <v>7.8125</v>
       </c>
       <c r="F144" t="n">
-        <v>6.38095238095238</v>
+        <v>8.928571428571429</v>
       </c>
       <c r="G144" t="n">
-        <v>7.677725118483413</v>
+        <v>0.6635071090047394</v>
       </c>
       <c r="H144" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
@@ -6047,7 +6047,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>45.0539381629429</v>
+        <v>37.85100710900474</v>
       </c>
     </row>
     <row r="145">
@@ -6056,37 +6056,37 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>6.635071090047393</v>
+        <v>9.722222222222223</v>
       </c>
       <c r="E145" t="n">
-        <v>15.28436018957346</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F145" t="n">
-        <v>9.809523809523808</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="G145" t="n">
-        <v>17.81990521327014</v>
+        <v>3.127962085308057</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>44.54886030241481</v>
+        <v>36.60018430753028</v>
       </c>
     </row>
     <row r="146">
@@ -6095,28 +6095,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>PIIND</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>13.74407582938389</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="E146" t="n">
-        <v>4.62085308056872</v>
+        <v>2.5</v>
       </c>
       <c r="F146" t="n">
-        <v>3.428571428571429</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="G146" t="n">
-        <v>7.109004739336493</v>
+        <v>2.748815165876777</v>
       </c>
       <c r="H146" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
@@ -6125,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>43.90250507786052</v>
+        <v>36.19325961032122</v>
       </c>
     </row>
     <row r="147">
@@ -6134,37 +6134,37 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Build-up</t>
         </is>
       </c>
       <c r="D147" t="n">
+        <v>3.611111111111111</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1.388888888888889</v>
+      </c>
+      <c r="F147" t="n">
+        <v>2.444444444444444</v>
+      </c>
+      <c r="G147" t="n">
         <v>1.895734597156398</v>
       </c>
-      <c r="E147" t="n">
-        <v>22.98578199052132</v>
-      </c>
-      <c r="F147" t="n">
-        <v>15.23809523809524</v>
-      </c>
-      <c r="G147" t="n">
-        <v>8.720379146919431</v>
-      </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>43.83999097269239</v>
+        <v>29.34017904160084</v>
       </c>
     </row>
     <row r="148">
@@ -6173,37 +6173,37 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>SAMMAANCAP</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>2.962085308056872</v>
+        <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>24.40758293838863</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>11.14285714285714</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>15.07109004739337</v>
+        <v>19.71563981042654</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I148" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>43.58361543669601</v>
+        <v>27.71563981042654</v>
       </c>
     </row>
     <row r="149">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -6221,28 +6221,28 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>6.398104265402843</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
-        <v>7.701421800947868</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>17.61904761904762</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>11.65876777251185</v>
+        <v>18.95734597156398</v>
       </c>
       <c r="H149" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I149" t="n">
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>43.37734145791018</v>
+        <v>26.95734597156398</v>
       </c>
     </row>
     <row r="150">
@@ -6251,37 +6251,37 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>AMBUJACEM</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>8.175355450236967</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>21.91943127962085</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>6.666666666666666</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>11.09004739336493</v>
+        <v>18.86255924170616</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I150" t="n">
         <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>42.85150078988941</v>
+        <v>26.86255924170616</v>
       </c>
     </row>
     <row r="151">
@@ -6290,37 +6290,37 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>9.24170616113744</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>15.87677725118483</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>13.42857142857143</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>9.004739336492891</v>
+        <v>18.67298578199052</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I151" t="n">
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>42.55179417738659</v>
+        <v>26.67298578199052</v>
       </c>
     </row>
     <row r="152">
@@ -6329,37 +6329,37 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>9.123222748815166</v>
+        <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>23.81516587677725</v>
+        <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>7.714285714285714</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>11.84834123222749</v>
+        <v>18.48341232227488</v>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I152" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>42.50101557210562</v>
+        <v>26.48341232227488</v>
       </c>
     </row>
     <row r="153">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6377,19 +6377,19 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>21.6824644549763</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>2.251184834123223</v>
+        <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>0.761904761904762</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>2.369668246445498</v>
+        <v>18.29383886255924</v>
       </c>
       <c r="H153" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
@@ -6398,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>42.06522229744979</v>
+        <v>26.29383886255924</v>
       </c>
     </row>
     <row r="154">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -6416,19 +6416,19 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>13.03317535545024</v>
+        <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>5.509478672985782</v>
+        <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>4.095238095238095</v>
+        <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>4.075829383886256</v>
+        <v>17.91469194312796</v>
       </c>
       <c r="H154" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>41.71372150756036</v>
+        <v>25.91469194312796</v>
       </c>
     </row>
     <row r="155">
@@ -6446,37 +6446,37 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>8.056872037914692</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>19.66824644549763</v>
+        <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>8.761904761904763</v>
+        <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>9.66824644549763</v>
+        <v>17.6303317535545</v>
       </c>
       <c r="H155" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>41.15526969081472</v>
+        <v>25.6303317535545</v>
       </c>
     </row>
     <row r="156">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6494,28 +6494,28 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>3.199052132701421</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>3.672985781990521</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>15.14285714285714</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>18.48341232227488</v>
+        <v>17.53554502369668</v>
       </c>
       <c r="H156" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>40.49830737982396</v>
+        <v>25.53554502369668</v>
       </c>
     </row>
     <row r="157">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>VMM</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6533,20 +6533,20 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>11.25592417061611</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>3.199052132701421</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>17.06161137440758</v>
+      </c>
+      <c r="H157" t="n">
         <v>8</v>
       </c>
-      <c r="G157" t="n">
-        <v>2.843601895734597</v>
-      </c>
-      <c r="H157" t="n">
-        <v>15</v>
-      </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
@@ -6554,7 +6554,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>40.29857819905213</v>
+        <v>25.06161137440758</v>
       </c>
     </row>
     <row r="158">
@@ -6563,37 +6563,37 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>7.819905213270142</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>6.69431279620853</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>18.76190476190476</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>6.919431279620854</v>
+        <v>16.2085308056872</v>
       </c>
       <c r="H158" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>40.19555405100429</v>
+        <v>24.2085308056872</v>
       </c>
     </row>
     <row r="159">
@@ -6602,37 +6602,37 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>4.265402843601896</v>
+        <v>0</v>
       </c>
       <c r="E159" t="n">
-        <v>22.39336492890995</v>
+        <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>1.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>17.25118483412322</v>
+        <v>16.11374407582938</v>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I159" t="n">
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>40.05280974949221</v>
+        <v>24.11374407582938</v>
       </c>
     </row>
     <row r="160">
@@ -6641,37 +6641,37 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>6.042654028436019</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>11.72985781990521</v>
+        <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>17.90476190476191</v>
+        <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>8.625592417061611</v>
+        <v>14.78672985781991</v>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>39.30286617016475</v>
+        <v>22.78672985781991</v>
       </c>
     </row>
     <row r="161">
@@ -6680,37 +6680,37 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>IREDA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>7.345971563981042</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>19.31279620853081</v>
+        <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>15.9047619047619</v>
+        <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>1.516587677725119</v>
+        <v>14.69194312796209</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>39.08011735499887</v>
+        <v>22.69194312796208</v>
       </c>
     </row>
     <row r="162">
@@ -6719,37 +6719,37 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.9478672985781991</v>
+        <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>21.56398104265403</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>2.380952380952381</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>18.5781990521327</v>
+        <v>13.93364928909953</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I162" t="n">
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>38.47099977431731</v>
+        <v>21.93364928909953</v>
       </c>
     </row>
     <row r="163">
@@ -6758,37 +6758,37 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>7.701421800947868</v>
+        <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>13.15165876777251</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>3.047619047619048</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>19.24170616113744</v>
+        <v>13.83886255924171</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>38.14240577747687</v>
+        <v>21.83886255924171</v>
       </c>
     </row>
     <row r="164">
@@ -6797,28 +6797,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>RVNL</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Short Covering</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>16.82464454976303</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
-        <v>1.777251184834123</v>
+        <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>3.523809523809524</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.947867298578199</v>
+        <v>13.74407582938389</v>
       </c>
       <c r="H164" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>38.07357255698489</v>
+        <v>21.74407582938389</v>
       </c>
     </row>
     <row r="165">
@@ -6836,37 +6836,37 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0.2369668246445498</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>12.66666666666667</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>10.14218009478673</v>
+        <v>13.27014218009479</v>
       </c>
       <c r="H165" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I165" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>38.04581358609795</v>
+        <v>21.27014218009479</v>
       </c>
     </row>
     <row r="166">
@@ -6875,37 +6875,37 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1.421800947867299</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>10.30805687203791</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>19.04761904761905</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>11.94312796208531</v>
+        <v>12.98578199052133</v>
       </c>
       <c r="H166" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>37.72060482960957</v>
+        <v>20.98578199052133</v>
       </c>
     </row>
     <row r="167">
@@ -6914,37 +6914,37 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>4.976303317535545</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>13.27014218009479</v>
+        <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>12.85714285714286</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>10.90047393364929</v>
+        <v>12.41706161137441</v>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>37.00406228842247</v>
+        <v>20.41706161137441</v>
       </c>
     </row>
     <row r="168">
@@ -6953,37 +6953,37 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>NHPC</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>8.767772511848342</v>
+        <v>0</v>
       </c>
       <c r="E168" t="n">
-        <v>13.86255924170616</v>
+        <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>18.19905213270142</v>
+        <v>11.65876777251185</v>
       </c>
       <c r="H168" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>36.40081245768449</v>
+        <v>19.65876777251185</v>
       </c>
     </row>
     <row r="169">
@@ -6992,37 +6992,37 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>7.227488151658767</v>
+        <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>16.46919431279621</v>
+        <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>15.45023696682464</v>
+        <v>11.56398104265403</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>36.14691943127962</v>
+        <v>19.56398104265403</v>
       </c>
     </row>
     <row r="170">
@@ -7031,37 +7031,37 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>COCHINSHIP</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>2.606635071090047</v>
+        <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>7.582938388625593</v>
+        <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>7.047619047619048</v>
+        <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>18.86255924170616</v>
+        <v>10.99526066350711</v>
       </c>
       <c r="H170" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I170" t="n">
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>36.09975174904085</v>
+        <v>18.99526066350711</v>
       </c>
     </row>
     <row r="171">
@@ -7070,37 +7070,37 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2.369668246445498</v>
+        <v>0</v>
       </c>
       <c r="E171" t="n">
-        <v>18.24644549763033</v>
+        <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>7.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>12.22748815165877</v>
+        <v>10.80568720379147</v>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>34.98645903859175</v>
+        <v>18.80568720379147</v>
       </c>
     </row>
     <row r="172">
@@ -7109,37 +7109,37 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1.658767772511848</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>24.64454976303318</v>
+        <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>10.57142857142857</v>
+        <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>7.014218009478673</v>
+        <v>10.42654028436019</v>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I172" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>33.88896411645227</v>
+        <v>18.42654028436019</v>
       </c>
     </row>
     <row r="173">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>RVNL</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -7157,28 +7157,28 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>6.161137440758294</v>
+        <v>0</v>
       </c>
       <c r="E173" t="n">
-        <v>0.7109004739336493</v>
+        <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>12.76190476190476</v>
+        <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>13.74407582938389</v>
+        <v>9.383886255924171</v>
       </c>
       <c r="H173" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I173" t="n">
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K173" t="n">
-        <v>33.37801850598059</v>
+        <v>17.38388625592417</v>
       </c>
     </row>
     <row r="174">
@@ -7187,37 +7187,37 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>4.502369668246446</v>
+        <v>0</v>
       </c>
       <c r="E174" t="n">
-        <v>14.8696682464455</v>
+        <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>15.52380952380952</v>
+        <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>3.222748815165877</v>
+        <v>8.436018957345972</v>
       </c>
       <c r="H174" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I174" t="n">
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>33.11859625366735</v>
+        <v>16.43601895734597</v>
       </c>
     </row>
     <row r="175">
@@ -7226,37 +7226,37 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>5.568720379146919</v>
+        <v>0</v>
       </c>
       <c r="E175" t="n">
-        <v>4.739336492890995</v>
+        <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>17.80952380952381</v>
+        <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>4.549763033175355</v>
+        <v>7.772511848341233</v>
       </c>
       <c r="H175" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>32.66734371473708</v>
+        <v>15.77251184834123</v>
       </c>
     </row>
     <row r="176">
@@ -7265,37 +7265,37 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>5.924170616113744</v>
+        <v>0</v>
       </c>
       <c r="E176" t="n">
-        <v>4.857819905213271</v>
+        <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>14.57142857142857</v>
+        <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>7.203791469194313</v>
+        <v>7.677725118483413</v>
       </c>
       <c r="H176" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I176" t="n">
         <v>0</v>
       </c>
       <c r="J176" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K176" t="n">
-        <v>32.5572105619499</v>
+        <v>15.67772511848341</v>
       </c>
     </row>
     <row r="177">
@@ -7304,37 +7304,37 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>8.293838862559241</v>
+        <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>16.11374407582938</v>
+        <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>5.80952380952381</v>
+        <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>6.066350710900474</v>
+        <v>7.582938388625592</v>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>31.28345745881291</v>
+        <v>15.58293838862559</v>
       </c>
     </row>
     <row r="178">
@@ -7343,37 +7343,37 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>2.488151658767773</v>
+        <v>0</v>
       </c>
       <c r="E178" t="n">
-        <v>19.43127962085308</v>
+        <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>13.64928909952607</v>
+        <v>7.203791469194313</v>
       </c>
       <c r="H178" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
       </c>
       <c r="J178" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>30.85443466486121</v>
+        <v>15.20379146919431</v>
       </c>
     </row>
     <row r="179">
@@ -7382,37 +7382,37 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1.540284360189573</v>
+        <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>13.68483412322275</v>
+        <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>3.904761904761905</v>
+        <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>16.6824644549763</v>
+        <v>7.109004739336493</v>
       </c>
       <c r="H179" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I179" t="n">
         <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>30.81234484315053</v>
+        <v>15.10900473933649</v>
       </c>
     </row>
     <row r="180">
@@ -7421,37 +7421,37 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>9.360189573459715</v>
+        <v>0</v>
       </c>
       <c r="E180" t="n">
-        <v>13.68483412322275</v>
+        <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>12.09523809523809</v>
+        <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.6635071090047394</v>
+        <v>6.919431279620854</v>
       </c>
       <c r="H180" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I180" t="n">
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>30.8037689009253</v>
+        <v>14.91943127962085</v>
       </c>
     </row>
     <row r="181">
@@ -7460,37 +7460,37 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>2.014218009478673</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>12.20379146919431</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>10.85714285714286</v>
+        <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>10.04739336492891</v>
+        <v>6.729857819905213</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>30.12254570074475</v>
+        <v>14.72985781990521</v>
       </c>
     </row>
     <row r="182">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -7508,19 +7508,19 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>11.37440758293839</v>
+        <v>0</v>
       </c>
       <c r="E182" t="n">
-        <v>0.2369668246445498</v>
+        <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>2.857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.4739336492890995</v>
+        <v>6.161137440758294</v>
       </c>
       <c r="H182" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I182" t="n">
         <v>0</v>
@@ -7529,7 +7529,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>29.9424509140149</v>
+        <v>14.16113744075829</v>
       </c>
     </row>
     <row r="183">
@@ -7538,37 +7538,37 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>5.213270142180095</v>
+        <v>0</v>
       </c>
       <c r="E183" t="n">
-        <v>22.27488151658768</v>
+        <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>1.523809523809524</v>
+        <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>5.592417061611375</v>
+        <v>5.687203791469194</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I183" t="n">
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>29.60437824418867</v>
+        <v>13.68720379146919</v>
       </c>
     </row>
     <row r="184">
@@ -7577,37 +7577,37 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>6.990521327014218</v>
+        <v>0</v>
       </c>
       <c r="E184" t="n">
-        <v>14.33649289099526</v>
+        <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>5.238095238095238</v>
+        <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>7.867298578199052</v>
+        <v>5.213270142180095</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>29.43240803430377</v>
+        <v>13.21327014218009</v>
       </c>
     </row>
     <row r="185">
@@ -7616,37 +7616,37 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>NAM-INDIA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>3.909952606635071</v>
+        <v>0</v>
       </c>
       <c r="E185" t="n">
-        <v>12.38151658767772</v>
+        <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>4.571428571428571</v>
+        <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>13.36492890995261</v>
+        <v>4.549763033175355</v>
       </c>
       <c r="H185" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I185" t="n">
         <v>0</v>
       </c>
       <c r="J185" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>29.22782667569398</v>
+        <v>12.54976303317536</v>
       </c>
     </row>
     <row r="186">
@@ -7655,37 +7655,37 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>3.554502369668247</v>
+        <v>0</v>
       </c>
       <c r="E186" t="n">
-        <v>11.37440758293839</v>
+        <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>17.23809523809524</v>
+        <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>1.706161137440758</v>
+        <v>4.454976303317536</v>
       </c>
       <c r="H186" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I186" t="n">
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>28.87316632814263</v>
+        <v>12.45497630331754</v>
       </c>
     </row>
     <row r="187">
@@ -7694,37 +7694,37 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>5.09478672985782</v>
+        <v>0</v>
       </c>
       <c r="E187" t="n">
-        <v>7.227488151658767</v>
+        <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>2.952380952380953</v>
+        <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>13.27014218009479</v>
+        <v>4.170616113744075</v>
       </c>
       <c r="H187" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I187" t="n">
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K187" t="n">
-        <v>28.54479801399233</v>
+        <v>12.17061611374407</v>
       </c>
     </row>
     <row r="188">
@@ -7733,37 +7733,37 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>8.530805687203792</v>
+        <v>0</v>
       </c>
       <c r="E188" t="n">
-        <v>14.57345971563981</v>
+        <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>3.714285714285714</v>
+        <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>6.540284360189573</v>
+        <v>4.075829383886256</v>
       </c>
       <c r="H188" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I188" t="n">
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>28.35883547731889</v>
+        <v>12.07582938388625</v>
       </c>
     </row>
     <row r="189">
@@ -7772,37 +7772,37 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>5.33175355450237</v>
+        <v>0</v>
       </c>
       <c r="E189" t="n">
-        <v>11.25592417061611</v>
+        <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>8.476190476190476</v>
+        <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>8.246445497630331</v>
+        <v>3.981042654028436</v>
       </c>
       <c r="H189" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>28.31031369893929</v>
+        <v>11.98104265402844</v>
       </c>
     </row>
     <row r="190">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7820,28 +7820,28 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1.303317535545024</v>
+        <v>0</v>
       </c>
       <c r="E190" t="n">
-        <v>3.554502369668247</v>
+        <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>14.66666666666667</v>
+        <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>8.436018957345972</v>
+        <v>3.696682464454976</v>
       </c>
       <c r="H190" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>27.96050552922591</v>
+        <v>11.69668246445498</v>
       </c>
     </row>
     <row r="191">
@@ -7850,37 +7850,37 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>3.436018957345972</v>
+        <v>0</v>
       </c>
       <c r="E191" t="n">
-        <v>4.324644549763033</v>
+        <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>1.904761904761905</v>
+        <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>17.53554502369668</v>
+        <v>3.601895734597156</v>
       </c>
       <c r="H191" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I191" t="n">
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>27.20097043556759</v>
+        <v>11.60189573459716</v>
       </c>
     </row>
     <row r="192">
@@ -7889,37 +7889,37 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>4.14691943127962</v>
+        <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>10.78199052132701</v>
+        <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>9.142857142857142</v>
+        <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>8.056872037914692</v>
+        <v>3.412322274881517</v>
       </c>
       <c r="H192" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I192" t="n">
         <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>27.12863913337847</v>
+        <v>11.41232227488152</v>
       </c>
     </row>
     <row r="193">
@@ -7928,37 +7928,37 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>9.004739336492891</v>
+        <v>0</v>
       </c>
       <c r="E193" t="n">
-        <v>10.66350710900474</v>
+        <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>9.047619047619047</v>
+        <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>2.464454976303317</v>
+        <v>3.033175355450237</v>
       </c>
       <c r="H193" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I193" t="n">
         <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K193" t="n">
-        <v>26.18032046942</v>
+        <v>11.03317535545024</v>
       </c>
     </row>
     <row r="194">
@@ -7967,37 +7967,37 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1.066350710900474</v>
+        <v>0</v>
       </c>
       <c r="E194" t="n">
-        <v>2.488151658767773</v>
+        <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>3.238095238095238</v>
+        <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>18.95734597156398</v>
+        <v>2.938388625592417</v>
       </c>
       <c r="H194" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I194" t="n">
         <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>25.74994357932746</v>
+        <v>10.93838862559242</v>
       </c>
     </row>
     <row r="195">
@@ -8006,37 +8006,37 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>5.80568720379147</v>
+        <v>0</v>
       </c>
       <c r="E195" t="n">
-        <v>2.014218009478673</v>
+        <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>11.90476190476191</v>
+        <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>5.213270142180095</v>
+        <v>2.843601895734597</v>
       </c>
       <c r="H195" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>24.93793726021214</v>
+        <v>10.8436018957346</v>
       </c>
     </row>
     <row r="196">
@@ -8045,37 +8045,37 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>0.1184834123222749</v>
+        <v>0</v>
       </c>
       <c r="E196" t="n">
-        <v>13.38862559241706</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>0.09523809523809525</v>
+        <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>14.50236966824645</v>
+        <v>2.654028436018958</v>
       </c>
       <c r="H196" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I196" t="n">
         <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>23.10471676822388</v>
+        <v>10.65402843601896</v>
       </c>
     </row>
     <row r="197">
@@ -8084,37 +8084,37 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>7.464454976303317</v>
+        <v>0</v>
       </c>
       <c r="E197" t="n">
-        <v>9.715639810426541</v>
+        <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>4.857142857142857</v>
+        <v>0</v>
       </c>
       <c r="G197" t="n">
-        <v>5.876777251184834</v>
+        <v>2.559241706161137</v>
       </c>
       <c r="H197" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I197" t="n">
         <v>0</v>
       </c>
       <c r="J197" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>22.91401489505755</v>
+        <v>10.55924170616114</v>
       </c>
     </row>
     <row r="198">
@@ -8123,37 +8123,37 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>3.317535545023697</v>
+        <v>0</v>
       </c>
       <c r="E198" t="n">
-        <v>5.983412322274882</v>
+        <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>9.904761904761905</v>
+        <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>3.696682464454976</v>
+        <v>2.369668246445498</v>
       </c>
       <c r="H198" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I198" t="n">
         <v>0</v>
       </c>
       <c r="J198" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>22.90239223651546</v>
+        <v>10.3696682464455</v>
       </c>
     </row>
     <row r="199">
@@ -8162,37 +8162,37 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0.8293838862559242</v>
+        <v>0</v>
       </c>
       <c r="E199" t="n">
-        <v>4.14691943127962</v>
+        <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>0.9523809523809523</v>
+        <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>14.78672985781991</v>
+        <v>2.180094786729858</v>
       </c>
       <c r="H199" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I199" t="n">
         <v>0</v>
       </c>
       <c r="J199" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>20.7154141277364</v>
+        <v>10.18009478672986</v>
       </c>
     </row>
     <row r="200">
@@ -8201,37 +8201,37 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0.4739336492890995</v>
+        <v>0</v>
       </c>
       <c r="E200" t="n">
-        <v>6.990521327014218</v>
+        <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>7.523809523809524</v>
+        <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>4.454976303317536</v>
+        <v>1.990521327014218</v>
       </c>
       <c r="H200" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I200" t="n">
         <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K200" t="n">
-        <v>19.44324080343038</v>
+        <v>9.990521327014218</v>
       </c>
     </row>
     <row r="201">
@@ -8240,37 +8240,37 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>2.132701421800948</v>
+        <v>0</v>
       </c>
       <c r="E201" t="n">
-        <v>17.18009478672986</v>
+        <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>2.476190476190476</v>
+        <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>2.085308056872038</v>
+        <v>1.800947867298578</v>
       </c>
       <c r="H201" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
       </c>
       <c r="J201" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>18.87429474159332</v>
+        <v>9.800947867298579</v>
       </c>
     </row>
     <row r="202">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -8288,28 +8288,28 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>4.62085308056872</v>
+        <v>0</v>
       </c>
       <c r="E202" t="n">
-        <v>2.725118483412322</v>
+        <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>2.095238095238095</v>
+        <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>9.383886255924171</v>
+        <v>1.327014218009479</v>
       </c>
       <c r="H202" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I202" t="n">
         <v>0</v>
       </c>
       <c r="J202" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>18.82509591514331</v>
+        <v>9.327014218009479</v>
       </c>
     </row>
     <row r="203">
@@ -8318,37 +8318,37 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>4.028436018957346</v>
+        <v>0</v>
       </c>
       <c r="E203" t="n">
-        <v>7.879146919431279</v>
+        <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>9.95260663507109</v>
+        <v>1.232227488151659</v>
       </c>
       <c r="H203" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I203" t="n">
         <v>0</v>
       </c>
       <c r="J203" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>18.19352290679305</v>
+        <v>9.232227488151658</v>
       </c>
     </row>
     <row r="204">
@@ -8357,37 +8357,37 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1.184834123222749</v>
+        <v>0</v>
       </c>
       <c r="E204" t="n">
-        <v>3.791469194312796</v>
+        <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>0.380952380952381</v>
+        <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>12.41706161137441</v>
+        <v>1.137440758293839</v>
       </c>
       <c r="H204" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I204" t="n">
         <v>0</v>
       </c>
       <c r="J204" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>17.77431730986233</v>
+        <v>9.137440758293838</v>
       </c>
     </row>
     <row r="205">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>GODFRYPHLP</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -8405,28 +8405,28 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>2.725118483412322</v>
+        <v>0</v>
       </c>
       <c r="E205" t="n">
-        <v>0.9478672985781991</v>
+        <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>12.47619047619048</v>
+        <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0.8530805687203792</v>
+        <v>1.042654028436019</v>
       </c>
       <c r="H205" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I205" t="n">
         <v>0</v>
       </c>
       <c r="J205" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K205" t="n">
-        <v>17.00225682690138</v>
+        <v>9.042654028436019</v>
       </c>
     </row>
     <row r="206">
@@ -8435,37 +8435,37 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>5.450236966824645</v>
+        <v>0</v>
       </c>
       <c r="E206" t="n">
-        <v>10.54502369668247</v>
+        <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>1.714285714285714</v>
+        <v>0</v>
       </c>
       <c r="G206" t="n">
-        <v>3.507109004739337</v>
+        <v>0.947867298578199</v>
       </c>
       <c r="H206" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I206" t="n">
         <v>0</v>
       </c>
       <c r="J206" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K206" t="n">
-        <v>16.21665538253216</v>
+        <v>8.947867298578199</v>
       </c>
     </row>
     <row r="207">
@@ -8474,37 +8474,37 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Short Build-up</t>
+          <t>Long Unwinding</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1.777251184834123</v>
+        <v>0</v>
       </c>
       <c r="E207" t="n">
-        <v>7.879146919431279</v>
+        <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>0.4761904761904762</v>
+        <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>9.857819905213269</v>
+        <v>0.8530805687203792</v>
       </c>
       <c r="H207" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I207" t="n">
         <v>0</v>
       </c>
       <c r="J207" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K207" t="n">
-        <v>14.99040848566915</v>
+        <v>8.85308056872038</v>
       </c>
     </row>
     <row r="208">
@@ -8513,37 +8513,37 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>GODFRYPHLP</t>
+          <t>FORCEMOT</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>4.857819905213271</v>
+        <v>0</v>
       </c>
       <c r="E208" t="n">
-        <v>3.080568720379147</v>
+        <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>5.619047619047619</v>
+        <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>1.042654028436019</v>
+        <v>0.5687203791469194</v>
       </c>
       <c r="H208" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I208" t="n">
         <v>0</v>
       </c>
       <c r="J208" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K208" t="n">
-        <v>14.60009027307606</v>
+        <v>8.568720379146919</v>
       </c>
     </row>
     <row r="209">
@@ -8552,37 +8552,37 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>4.739336492890995</v>
+        <v>0</v>
       </c>
       <c r="E209" t="n">
-        <v>3.909952606635071</v>
+        <v>0</v>
       </c>
       <c r="F209" t="n">
-        <v>4.190476190476191</v>
+        <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>1.327014218009479</v>
+        <v>0.4739336492890995</v>
       </c>
       <c r="H209" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I209" t="n">
         <v>0</v>
       </c>
       <c r="J209" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K209" t="n">
-        <v>14.16677950801174</v>
+        <v>8.4739336492891</v>
       </c>
     </row>
     <row r="210">
@@ -8591,37 +8591,37 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>PAGEIND</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>3.080568720379147</v>
+        <v>0</v>
       </c>
       <c r="E210" t="n">
-        <v>2.843601895734597</v>
+        <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="G210" t="n">
-        <v>3.033175355450237</v>
+        <v>0.2843601895734597</v>
       </c>
       <c r="H210" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I210" t="n">
         <v>0</v>
       </c>
       <c r="J210" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K210" t="n">
-        <v>9.624012638230649</v>
+        <v>8.28436018957346</v>
       </c>
     </row>
     <row r="211">
@@ -8630,37 +8630,37 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0.3554502369668247</v>
+        <v>0</v>
       </c>
       <c r="E211" t="n">
-        <v>6.516587677725119</v>
+        <v>0</v>
       </c>
       <c r="F211" t="n">
-        <v>0.1904761904761905</v>
+        <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>2.559241706161137</v>
+        <v>0.1895734597156398</v>
       </c>
       <c r="H211" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I211" t="n">
         <v>0</v>
       </c>
       <c r="J211" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K211" t="n">
-        <v>9.621755811329272</v>
+        <v>8.189573459715639</v>
       </c>
     </row>
     <row r="212">
@@ -8669,37 +8669,37 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>SHREECEM</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Long Unwinding</t>
+          <t>Short Covering</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>2.251184834123223</v>
+        <v>0</v>
       </c>
       <c r="E212" t="n">
-        <v>1.184834123222749</v>
+        <v>0</v>
       </c>
       <c r="F212" t="n">
-        <v>2.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>1.800947867298578</v>
+        <v>0.09478672985781991</v>
       </c>
       <c r="H212" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I212" t="n">
         <v>0</v>
       </c>
       <c r="J212" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="K212" t="n">
-        <v>7.903633491311217</v>
+        <v>8.09478672985782</v>
       </c>
     </row>
   </sheetData>

--- a/Output/R_FACTOR.xlsx
+++ b/Output/R_FACTOR.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K212"/>
+  <dimension ref="A1:L212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,20 +454,25 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Delivery Score</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Bonus Score</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Conviction Score</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Momentum Score</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>R Factor</t>
         </is>
@@ -500,15 +505,18 @@
         <v>19.14691943127962</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>3.672985781990521</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>5</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>104.480252764613</v>
       </c>
     </row>
@@ -539,15 +547,18 @@
         <v>18.5781990521327</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>3.246445497630332</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>102.3281990521327</v>
       </c>
     </row>
@@ -578,15 +589,18 @@
         <v>15.07109004739337</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>1.872037914691943</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
       </c>
       <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="n">
         <v>96.76751861882194</v>
       </c>
     </row>
@@ -617,15 +631,18 @@
         <v>19.33649289099526</v>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
+        <v>1.943127962085308</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>5</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>96.55871511321747</v>
       </c>
     </row>
@@ -656,15 +673,18 @@
         <v>17.25118483412322</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>2.701421800947867</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>96.5368991198375</v>
       </c>
     </row>
@@ -695,15 +715,18 @@
         <v>7.488151658767772</v>
       </c>
       <c r="H7" t="n">
-        <v>20</v>
+        <v>1.729857819905213</v>
       </c>
       <c r="I7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" t="n">
         <v>5</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>96.29370721432333</v>
       </c>
     </row>
@@ -734,15 +757,18 @@
         <v>12.32227488151659</v>
       </c>
       <c r="H8" t="n">
-        <v>20</v>
+        <v>2.298578199052133</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
         <v>5</v>
       </c>
       <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
         <v>94.73894154818325</v>
       </c>
     </row>
@@ -773,15 +799,18 @@
         <v>13.64928909952607</v>
       </c>
       <c r="H9" t="n">
-        <v>20</v>
+        <v>3.886255924170616</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>5</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>93.11357481381178</v>
       </c>
     </row>
@@ -812,15 +841,18 @@
         <v>17.34597156398104</v>
       </c>
       <c r="H10" t="n">
-        <v>20</v>
+        <v>3.862559241706161</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>5</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>92.95708267509215</v>
       </c>
     </row>
@@ -851,15 +883,18 @@
         <v>10.14218009478673</v>
       </c>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>1.990521327014218</v>
       </c>
       <c r="I11" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" t="n">
         <v>5</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>92.91003723764388</v>
       </c>
     </row>
@@ -890,15 +925,18 @@
         <v>14.50236966824645</v>
       </c>
       <c r="H12" t="n">
-        <v>20</v>
+        <v>0.2369668246445497</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>5</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>91.64522681110358</v>
       </c>
     </row>
@@ -929,15 +967,18 @@
         <v>19.90521327014218</v>
       </c>
       <c r="H13" t="n">
-        <v>20</v>
+        <v>0.6161137440758293</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>91.51235612728503</v>
       </c>
     </row>
@@ -968,15 +1009,18 @@
         <v>16.77725118483412</v>
       </c>
       <c r="H14" t="n">
-        <v>20</v>
+        <v>3.767772511848341</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>5</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>91.0550289626119</v>
       </c>
     </row>
@@ -1007,15 +1051,18 @@
         <v>14.40758293838863</v>
       </c>
       <c r="H15" t="n">
-        <v>20</v>
+        <v>4.075829383886256</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>5</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>90.30044008124577</v>
       </c>
     </row>
@@ -1046,15 +1093,18 @@
         <v>17.72511848341232</v>
       </c>
       <c r="H16" t="n">
-        <v>20</v>
+        <v>1.113744075829384</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>5</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>88.88583276912661</v>
       </c>
     </row>
@@ -1085,15 +1135,18 @@
         <v>7.014218009478673</v>
       </c>
       <c r="H17" t="n">
-        <v>20</v>
+        <v>3.341232227488152</v>
       </c>
       <c r="I17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" t="n">
         <v>5</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>88.44278943805011</v>
       </c>
     </row>
@@ -1124,15 +1177,18 @@
         <v>11.75355450236967</v>
       </c>
       <c r="H18" t="n">
-        <v>20</v>
+        <v>1.421800947867299</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>87.86466561348078</v>
       </c>
     </row>
@@ -1163,15 +1219,18 @@
         <v>5.308056872037915</v>
       </c>
       <c r="H19" t="n">
-        <v>20</v>
+        <v>2.725118483412322</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>87.41916798314902</v>
       </c>
     </row>
@@ -1202,15 +1261,18 @@
         <v>16.6824644549763</v>
       </c>
       <c r="H20" t="n">
-        <v>20</v>
+        <v>0.6398104265402843</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
         <v>5</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>87.17353588354773</v>
       </c>
     </row>
@@ -1241,15 +1303,18 @@
         <v>11.27962085308057</v>
       </c>
       <c r="H21" t="n">
-        <v>20</v>
+        <v>3.696682464454976</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>87.14073196419169</v>
       </c>
     </row>
@@ -1280,15 +1345,18 @@
         <v>15.35545023696683</v>
       </c>
       <c r="H22" t="n">
-        <v>20</v>
+        <v>0.3791469194312796</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>5</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>86.35545023696682</v>
       </c>
     </row>
@@ -1319,15 +1387,18 @@
         <v>16.96682464454976</v>
       </c>
       <c r="H23" t="n">
-        <v>20</v>
+        <v>1.919431279620853</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>83.63349131121643</v>
       </c>
     </row>
@@ -1358,15 +1429,18 @@
         <v>11.37440758293839</v>
       </c>
       <c r="H24" t="n">
-        <v>20</v>
+        <v>3.791469194312796</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>83.31885202738283</v>
       </c>
     </row>
@@ -1397,15 +1471,18 @@
         <v>12.22748815165877</v>
       </c>
       <c r="H25" t="n">
-        <v>20</v>
+        <v>3.436018957345972</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
         <v>5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>83.20963100880164</v>
       </c>
     </row>
@@ -1436,15 +1513,18 @@
         <v>14.31279620853081</v>
       </c>
       <c r="H26" t="n">
-        <v>20</v>
+        <v>4.90521327014218</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>5</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>83.2016850974197</v>
       </c>
     </row>
@@ -1475,15 +1555,18 @@
         <v>11.46919431279621</v>
       </c>
       <c r="H27" t="n">
-        <v>20</v>
+        <v>4.265402843601896</v>
       </c>
       <c r="I27" t="n">
+        <v>20</v>
+      </c>
+      <c r="J27" t="n">
         <v>5</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>82.91363875724065</v>
       </c>
     </row>
@@ -1514,15 +1597,18 @@
         <v>12.89099526066351</v>
       </c>
       <c r="H28" t="n">
-        <v>20</v>
+        <v>0.6635071090047394</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>5</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>79.33543970510794</v>
       </c>
     </row>
@@ -1553,15 +1639,18 @@
         <v>16.87203791469194</v>
       </c>
       <c r="H29" t="n">
-        <v>20</v>
+        <v>2.132701421800948</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
         <v>5</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>79.28275220040624</v>
       </c>
     </row>
@@ -1592,15 +1681,18 @@
         <v>14.02843601895735</v>
       </c>
       <c r="H30" t="n">
-        <v>20</v>
+        <v>3.151658767772512</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>5</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>78.05621379673512</v>
       </c>
     </row>
@@ -1631,15 +1723,18 @@
         <v>8.720379146919431</v>
       </c>
       <c r="H31" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>76.93466486120515</v>
       </c>
     </row>
@@ -1670,15 +1765,18 @@
         <v>5.592417061611375</v>
       </c>
       <c r="H32" t="n">
-        <v>20</v>
+        <v>2.606635071090047</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>76.93170277589709</v>
       </c>
     </row>
@@ -1709,15 +1807,18 @@
         <v>20</v>
       </c>
       <c r="H33" t="n">
-        <v>20</v>
+        <v>0.1421800947867299</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
         <v>76.88888888888889</v>
       </c>
     </row>
@@ -1748,15 +1849,18 @@
         <v>6.445497630331753</v>
       </c>
       <c r="H34" t="n">
-        <v>20</v>
+        <v>1.350710900473934</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>75.8899420747762</v>
       </c>
     </row>
@@ -1787,15 +1891,18 @@
         <v>14.59715639810426</v>
       </c>
       <c r="H35" t="n">
-        <v>20</v>
+        <v>3.981042654028436</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>75.87493417588205</v>
       </c>
     </row>
@@ -1826,15 +1933,18 @@
         <v>19.0521327014218</v>
       </c>
       <c r="H36" t="n">
-        <v>20</v>
+        <v>4.407582938388625</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>5</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>75.27435492364403</v>
       </c>
     </row>
@@ -1865,15 +1975,18 @@
         <v>18.1042654028436</v>
       </c>
       <c r="H37" t="n">
-        <v>20</v>
+        <v>4.786729857819905</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>75.27093206951027</v>
       </c>
     </row>
@@ -1904,15 +2017,18 @@
         <v>13.36492890995261</v>
       </c>
       <c r="H38" t="n">
-        <v>20</v>
+        <v>2.440758293838862</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>5</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>75.23992890995261</v>
       </c>
     </row>
@@ -1943,15 +2059,18 @@
         <v>9.289099526066352</v>
       </c>
       <c r="H39" t="n">
-        <v>20</v>
+        <v>2.061611374407583</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>75.23354397051079</v>
       </c>
     </row>
@@ -1982,15 +2101,18 @@
         <v>9.57345971563981</v>
       </c>
       <c r="H40" t="n">
-        <v>20</v>
+        <v>2.511848341232227</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>75.12901527119537</v>
       </c>
     </row>
@@ -2021,15 +2143,18 @@
         <v>15.7345971563981</v>
       </c>
       <c r="H41" t="n">
-        <v>20</v>
+        <v>4.052132701421801</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>5</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>74.45681937862032</v>
       </c>
     </row>
@@ -2060,15 +2185,18 @@
         <v>14.88151658767773</v>
       </c>
       <c r="H42" t="n">
-        <v>20</v>
+        <v>4.431279620853081</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
         <v>74.43508801624915</v>
       </c>
     </row>
@@ -2099,15 +2227,18 @@
         <v>1.611374407582938</v>
       </c>
       <c r="H43" t="n">
-        <v>20</v>
+        <v>2.938388625592417</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>74.27804107424961</v>
       </c>
     </row>
@@ -2138,15 +2269,18 @@
         <v>7.393364928909953</v>
       </c>
       <c r="H44" t="n">
-        <v>20</v>
+        <v>4.857819905213271</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>74.22669826224329</v>
       </c>
     </row>
@@ -2177,15 +2311,18 @@
         <v>19.81042654028436</v>
       </c>
       <c r="H45" t="n">
-        <v>20</v>
+        <v>1.445497630331753</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>5</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>73.92153765139547</v>
       </c>
     </row>
@@ -2216,15 +2353,18 @@
         <v>12.13270142180095</v>
       </c>
       <c r="H46" t="n">
-        <v>20</v>
+        <v>0.8293838862559242</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
         <v>73.57714586624539</v>
       </c>
     </row>
@@ -2255,15 +2395,18 @@
         <v>18.76777251184834</v>
       </c>
       <c r="H47" t="n">
-        <v>20</v>
+        <v>4.241706161137441</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
         <v>73.57332806740391</v>
       </c>
     </row>
@@ -2294,15 +2437,18 @@
         <v>15.54502369668247</v>
       </c>
       <c r="H48" t="n">
-        <v>20</v>
+        <v>0.2606635071090047</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>5</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>73.43391258557135</v>
       </c>
     </row>
@@ -2333,15 +2479,18 @@
         <v>15.45023696682464</v>
       </c>
       <c r="H49" t="n">
-        <v>20</v>
+        <v>4.691943127962086</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
         <v>72.68237982396751</v>
       </c>
     </row>
@@ -2372,15 +2521,18 @@
         <v>6.635071090047393</v>
       </c>
       <c r="H50" t="n">
-        <v>20</v>
+        <v>1.895734597156398</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
         <v>72.46840442338072</v>
       </c>
     </row>
@@ -2411,15 +2563,18 @@
         <v>12.51184834123223</v>
       </c>
       <c r="H51" t="n">
-        <v>20</v>
+        <v>0.4976303317535545</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
         <v>72.45629278567667</v>
       </c>
     </row>
@@ -2450,15 +2605,18 @@
         <v>13.55450236966825</v>
       </c>
       <c r="H52" t="n">
-        <v>20</v>
+        <v>3.317535545023697</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
         <v>72.33228014744603</v>
       </c>
     </row>
@@ -2489,15 +2647,18 @@
         <v>9.763033175355449</v>
       </c>
       <c r="H53" t="n">
-        <v>20</v>
+        <v>4.644549763033176</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
         <v>72.26303317535545</v>
       </c>
     </row>
@@ -2528,15 +2689,18 @@
         <v>19.43127962085308</v>
       </c>
       <c r="H54" t="n">
-        <v>20</v>
+        <v>2.488151658767773</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
         <v>71.75270819228166</v>
       </c>
     </row>
@@ -2567,15 +2731,18 @@
         <v>2.085308056872038</v>
       </c>
       <c r="H55" t="n">
-        <v>20</v>
+        <v>1.516587677725119</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
         <v>71.54959377115776</v>
       </c>
     </row>
@@ -2606,15 +2773,18 @@
         <v>9.857819905213269</v>
       </c>
       <c r="H56" t="n">
-        <v>20</v>
+        <v>1.848341232227488</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
         <v>71.24174847664185</v>
       </c>
     </row>
@@ -2645,15 +2815,18 @@
         <v>13.17535545023697</v>
       </c>
       <c r="H57" t="n">
-        <v>20</v>
+        <v>2.559241706161137</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>5</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>71.23091100579252</v>
       </c>
     </row>
@@ -2684,15 +2857,18 @@
         <v>14.12322274881516</v>
       </c>
       <c r="H58" t="n">
-        <v>20</v>
+        <v>3.033175355450237</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
         <v>5</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>71.06766719325961</v>
       </c>
     </row>
@@ -2723,15 +2899,18 @@
         <v>15.63981042654028</v>
       </c>
       <c r="H59" t="n">
-        <v>20</v>
+        <v>2.535545023696683</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
         <v>71.02869931542917</v>
       </c>
     </row>
@@ -2762,15 +2941,18 @@
         <v>12.60663507109005</v>
       </c>
       <c r="H60" t="n">
-        <v>20</v>
+        <v>4.549763033175355</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
         <v>70.91020649966148</v>
       </c>
     </row>
@@ -2801,15 +2983,18 @@
         <v>9.19431279620853</v>
       </c>
       <c r="H61" t="n">
-        <v>20</v>
+        <v>1.374407582938389</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
         <v>70.58320168509741</v>
       </c>
     </row>
@@ -2840,15 +3025,18 @@
         <v>10.33175355450237</v>
       </c>
       <c r="H62" t="n">
-        <v>20</v>
+        <v>0.9004739336492891</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
         <v>70.44286466561348</v>
       </c>
     </row>
@@ -2879,15 +3067,18 @@
         <v>16.01895734597156</v>
       </c>
       <c r="H63" t="n">
-        <v>20</v>
+        <v>3.815165876777251</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
         <v>69.67967163168585</v>
       </c>
     </row>
@@ -2918,15 +3109,18 @@
         <v>4.360189573459715</v>
       </c>
       <c r="H64" t="n">
-        <v>20</v>
+        <v>2.369668246445498</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
         <v>69.58241179568194</v>
       </c>
     </row>
@@ -2957,15 +3151,18 @@
         <v>18.38862559241706</v>
       </c>
       <c r="H65" t="n">
-        <v>20</v>
+        <v>1.966824644549763</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
         <v>69.16640337019484</v>
       </c>
     </row>
@@ -2996,15 +3193,18 @@
         <v>17.81990521327014</v>
       </c>
       <c r="H66" t="n">
-        <v>20</v>
+        <v>2.156398104265403</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
         <v>69.15919092755585</v>
       </c>
     </row>
@@ -3035,15 +3235,18 @@
         <v>15.16587677725118</v>
       </c>
       <c r="H67" t="n">
-        <v>20</v>
+        <v>2.890995260663507</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
         <v>69.11032122169563</v>
       </c>
     </row>
@@ -3074,15 +3277,18 @@
         <v>13.08056872037915</v>
       </c>
       <c r="H68" t="n">
-        <v>20</v>
+        <v>4.739336492890995</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
         <v>5</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
         <v>69.02501316482359</v>
       </c>
     </row>
@@ -3113,15 +3319,18 @@
         <v>11.84834123222749</v>
       </c>
       <c r="H69" t="n">
-        <v>20</v>
+        <v>4.976303317535545</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
         <v>68.99119837508462</v>
       </c>
     </row>
@@ -3152,15 +3361,18 @@
         <v>6.350710900473934</v>
       </c>
       <c r="H70" t="n">
-        <v>20</v>
+        <v>4.14691943127962</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
         <v>68.57293312269616</v>
       </c>
     </row>
@@ -3191,15 +3403,18 @@
         <v>18.19905213270142</v>
       </c>
       <c r="H71" t="n">
-        <v>20</v>
+        <v>1.706161137440758</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
         <v>68.28833784698713</v>
       </c>
     </row>
@@ -3230,15 +3445,18 @@
         <v>11.09004739336493</v>
       </c>
       <c r="H72" t="n">
-        <v>20</v>
+        <v>3.175355450236967</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
         <v>68.05433310765065</v>
       </c>
     </row>
@@ -3269,15 +3487,18 @@
         <v>14.21800947867299</v>
       </c>
       <c r="H73" t="n">
-        <v>20</v>
+        <v>4.597156398104265</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
         <v>5</v>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" t="n">
         <v>67.88467614533965</v>
       </c>
     </row>
@@ -3308,15 +3529,18 @@
         <v>10.23696682464455</v>
       </c>
       <c r="H74" t="n">
-        <v>20</v>
+        <v>2.014218009478673</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
         <v>67.84807793575567</v>
       </c>
     </row>
@@ -3347,15 +3571,18 @@
         <v>19.24170616113744</v>
       </c>
       <c r="H75" t="n">
-        <v>20</v>
+        <v>3.483412322274881</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
         <v>67.81313473256601</v>
       </c>
     </row>
@@ -3386,15 +3613,18 @@
         <v>10.71090047393365</v>
       </c>
       <c r="H76" t="n">
-        <v>20</v>
+        <v>0.3317535545023697</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
         <v>67.76645602948921</v>
       </c>
     </row>
@@ -3425,15 +3655,18 @@
         <v>4.928909952606634</v>
       </c>
       <c r="H77" t="n">
-        <v>20</v>
+        <v>1.682464454976303</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
         <v>67.37335439705107</v>
       </c>
     </row>
@@ -3464,15 +3697,18 @@
         <v>3.791469194312796</v>
       </c>
       <c r="H78" t="n">
-        <v>20</v>
+        <v>3.590047393364929</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
         <v>66.73591363875724</v>
       </c>
     </row>
@@ -3503,15 +3739,18 @@
         <v>17.1563981042654</v>
       </c>
       <c r="H79" t="n">
-        <v>20</v>
+        <v>2.748815165876777</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
         <v>66.54528699315429</v>
       </c>
     </row>
@@ -3542,15 +3781,18 @@
         <v>8.909952606635072</v>
       </c>
       <c r="H80" t="n">
-        <v>20</v>
+        <v>4.928909952606634</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
         <v>66.52106371774619</v>
       </c>
     </row>
@@ -3581,15 +3823,18 @@
         <v>17.44075829383886</v>
       </c>
       <c r="H81" t="n">
-        <v>20</v>
+        <v>3.412322274881517</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
         <v>66.10147257955315</v>
       </c>
     </row>
@@ -3620,15 +3865,18 @@
         <v>3.317535545023697</v>
       </c>
       <c r="H82" t="n">
-        <v>20</v>
+        <v>1.800947867298578</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
         <v>65.70642443391259</v>
       </c>
     </row>
@@ -3659,15 +3907,18 @@
         <v>19.62085308056872</v>
       </c>
       <c r="H83" t="n">
-        <v>20</v>
+        <v>4.194312796208531</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
         <v>65.25974196945761</v>
       </c>
     </row>
@@ -3698,15 +3949,18 @@
         <v>10.04739336492891</v>
       </c>
       <c r="H84" t="n">
-        <v>20</v>
+        <v>3.590047393364929</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
         <v>65.13667907921462</v>
       </c>
     </row>
@@ -3737,15 +3991,18 @@
         <v>9.95260663507109</v>
       </c>
       <c r="H85" t="n">
-        <v>20</v>
+        <v>2.819905213270142</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
         <v>64.90796377792825</v>
       </c>
     </row>
@@ -3776,15 +4033,18 @@
         <v>18.00947867298578</v>
       </c>
       <c r="H86" t="n">
-        <v>20</v>
+        <v>3.744075829383886</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
       </c>
       <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
         <v>64.56503422854134</v>
       </c>
     </row>
@@ -3815,15 +4075,18 @@
         <v>5.118483412322274</v>
       </c>
       <c r="H87" t="n">
-        <v>20</v>
+        <v>2.855450236966824</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
         <v>64.06292785676672</v>
       </c>
     </row>
@@ -3854,15 +4117,18 @@
         <v>4.834123222748815</v>
       </c>
       <c r="H88" t="n">
-        <v>20</v>
+        <v>4.028436018957346</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
       <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
         <v>63.7230121116377</v>
       </c>
     </row>
@@ -3893,15 +4159,18 @@
         <v>15.260663507109</v>
       </c>
       <c r="H89" t="n">
-        <v>20</v>
+        <v>1.563981042654028</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
         <v>63.65352064996614</v>
       </c>
     </row>
@@ -3932,15 +4201,18 @@
         <v>7.298578199052132</v>
       </c>
       <c r="H90" t="n">
-        <v>20</v>
+        <v>4.810426540284361</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
         <v>63.57635597682991</v>
       </c>
     </row>
@@ -3971,15 +4243,18 @@
         <v>9.478672985781991</v>
       </c>
       <c r="H91" t="n">
-        <v>20</v>
+        <v>2.109004739336493</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
         <v>63.42311743022643</v>
       </c>
     </row>
@@ -4010,15 +4285,18 @@
         <v>7.962085308056873</v>
       </c>
       <c r="H92" t="n">
-        <v>20</v>
+        <v>4.123222748815166</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
         <v>63.29541864139021</v>
       </c>
     </row>
@@ -4049,15 +4327,18 @@
         <v>19.5260663507109</v>
       </c>
       <c r="H93" t="n">
-        <v>20</v>
+        <v>3.933649289099526</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
         <v>62.85939968404423</v>
       </c>
     </row>
@@ -4088,15 +4369,18 @@
         <v>9.66824644549763</v>
       </c>
       <c r="H94" t="n">
-        <v>20</v>
+        <v>2.677725118483412</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
         <v>62.52538930264049</v>
       </c>
     </row>
@@ -4127,15 +4411,18 @@
         <v>3.886255924170616</v>
       </c>
       <c r="H95" t="n">
-        <v>20</v>
+        <v>3.649289099526066</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
         <v>62.19181147972618</v>
       </c>
     </row>
@@ -4166,15 +4453,18 @@
         <v>16.49289099526066</v>
       </c>
       <c r="H96" t="n">
-        <v>20</v>
+        <v>2.085308056872038</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
         <v>61.88177988414955</v>
       </c>
     </row>
@@ -4205,15 +4495,18 @@
         <v>15.82938388625592</v>
       </c>
       <c r="H97" t="n">
-        <v>20</v>
+        <v>2.796208530805687</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
         <v>61.77382833070037</v>
       </c>
     </row>
@@ -4244,15 +4537,18 @@
         <v>4.644549763033176</v>
       </c>
       <c r="H98" t="n">
-        <v>20</v>
+        <v>4.218009478672986</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
         <v>61.70010531858873</v>
       </c>
     </row>
@@ -4283,15 +4579,18 @@
         <v>8.530805687203792</v>
       </c>
       <c r="H99" t="n">
-        <v>20</v>
+        <v>4.834123222748815</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
         <v>61.47723425863236</v>
       </c>
     </row>
@@ -4322,15 +4621,18 @@
         <v>10.61611374407583</v>
       </c>
       <c r="H100" t="n">
-        <v>20</v>
+        <v>1.777251184834123</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
         <v>61.15182802979012</v>
       </c>
     </row>
@@ -4361,15 +4663,18 @@
         <v>16.58767772511848</v>
       </c>
       <c r="H101" t="n">
-        <v>20</v>
+        <v>4.170616113744075</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
       </c>
       <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
         <v>60.75434439178515</v>
       </c>
     </row>
@@ -4400,15 +4705,18 @@
         <v>12.79620853080569</v>
       </c>
       <c r="H102" t="n">
-        <v>20</v>
+        <v>4.95260663507109</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
       </c>
       <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
         <v>60.74065297525013</v>
       </c>
     </row>
@@ -4439,15 +4747,18 @@
         <v>10.52132701421801</v>
       </c>
       <c r="H103" t="n">
-        <v>20</v>
+        <v>1.398104265402844</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
         <v>60.57688256977356</v>
       </c>
     </row>
@@ -4478,15 +4789,18 @@
         <v>7.867298578199052</v>
       </c>
       <c r="H104" t="n">
-        <v>20</v>
+        <v>1.492890995260663</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
         <v>60.45658429248477</v>
       </c>
     </row>
@@ -4517,15 +4831,18 @@
         <v>1.421800947867299</v>
       </c>
       <c r="H105" t="n">
-        <v>20</v>
+        <v>4.33649289099526</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
       </c>
       <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
         <v>59.97735650342285</v>
       </c>
     </row>
@@ -4556,15 +4873,18 @@
         <v>8.151658767772512</v>
       </c>
       <c r="H106" t="n">
-        <v>20</v>
+        <v>4.66824644549763</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
       </c>
       <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
         <v>59.87388098999473</v>
       </c>
     </row>
@@ -4595,15 +4915,18 @@
         <v>16.39810426540284</v>
       </c>
       <c r="H107" t="n">
-        <v>20</v>
+        <v>1.303317535545024</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
       </c>
       <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
         <v>59.70167569397427</v>
       </c>
     </row>
@@ -4634,15 +4957,18 @@
         <v>15.92417061611375</v>
       </c>
       <c r="H108" t="n">
-        <v>20</v>
+        <v>3.056872037914692</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
         <v>59.42417061611374</v>
       </c>
     </row>
@@ -4673,15 +4999,18 @@
         <v>10.90047393364929</v>
       </c>
       <c r="H109" t="n">
-        <v>20</v>
+        <v>1.184834123222749</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
         <v>59.29333107650643</v>
       </c>
     </row>
@@ -4712,15 +5041,18 @@
         <v>5.971563981042653</v>
       </c>
       <c r="H110" t="n">
-        <v>20</v>
+        <v>1.161137440758294</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
         <v>59.08267509215376</v>
       </c>
     </row>
@@ -4751,15 +5083,18 @@
         <v>6.824644549763033</v>
       </c>
       <c r="H111" t="n">
-        <v>20</v>
+        <v>4.454976303317536</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
         <v>58.93575566087414</v>
       </c>
     </row>
@@ -4790,15 +5125,18 @@
         <v>8.81516587677725</v>
       </c>
       <c r="H112" t="n">
-        <v>20</v>
+        <v>0.02369668246445498</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
         <v>58.37072143233281</v>
       </c>
     </row>
@@ -4829,15 +5167,18 @@
         <v>5.023696682464455</v>
       </c>
       <c r="H113" t="n">
-        <v>20</v>
+        <v>0.5687203791469194</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
         <v>58.07925223802001</v>
       </c>
     </row>
@@ -4868,15 +5209,18 @@
         <v>8.056872037914692</v>
       </c>
       <c r="H114" t="n">
-        <v>20</v>
+        <v>1.587677725118483</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
       <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
         <v>57.52115775220041</v>
       </c>
     </row>
@@ -4907,15 +5251,18 @@
         <v>11.94312796208531</v>
       </c>
       <c r="H115" t="n">
-        <v>20</v>
+        <v>3.530805687203791</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
       </c>
       <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
         <v>57.21098510494245</v>
       </c>
     </row>
@@ -4946,15 +5293,18 @@
         <v>16.30331753554502</v>
       </c>
       <c r="H116" t="n">
-        <v>20</v>
+        <v>0.3554502369668247</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
         <v>57.19617467840217</v>
       </c>
     </row>
@@ -4985,15 +5335,18 @@
         <v>8.246445497630331</v>
       </c>
       <c r="H117" t="n">
-        <v>20</v>
+        <v>3.080568720379147</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
         <v>56.55001692620176</v>
       </c>
     </row>
@@ -5024,15 +5377,18 @@
         <v>6.066350710900474</v>
       </c>
       <c r="H118" t="n">
-        <v>20</v>
+        <v>2.274881516587678</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
         <v>56.06635071090047</v>
       </c>
     </row>
@@ -5063,15 +5419,18 @@
         <v>3.507109004739337</v>
       </c>
       <c r="H119" t="n">
-        <v>20</v>
+        <v>3.222748815165877</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
       </c>
       <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
         <v>55.7392518618822</v>
       </c>
     </row>
@@ -5102,15 +5461,18 @@
         <v>6.540284360189573</v>
       </c>
       <c r="H120" t="n">
-        <v>20</v>
+        <v>2.962085308056872</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
       </c>
       <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
         <v>55.64742721733243</v>
       </c>
     </row>
@@ -5141,15 +5503,18 @@
         <v>5.402843601895735</v>
       </c>
       <c r="H121" t="n">
-        <v>20</v>
+        <v>4.57345971563981</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
       </c>
       <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
         <v>54.86712931618145</v>
       </c>
     </row>
@@ -5180,15 +5545,18 @@
         <v>8.341232227488151</v>
       </c>
       <c r="H122" t="n">
-        <v>20</v>
+        <v>4.312796208530806</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
       </c>
       <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
         <v>54.11901000526593</v>
       </c>
     </row>
@@ -5219,15 +5587,18 @@
         <v>14.97630331753554</v>
       </c>
       <c r="H123" t="n">
-        <v>20</v>
+        <v>4.62085308056872</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
       <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
         <v>54.0318588730911</v>
       </c>
     </row>
@@ -5258,15 +5629,18 @@
         <v>12.03791469194313</v>
       </c>
       <c r="H124" t="n">
-        <v>20</v>
+        <v>0.4028436018957346</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
       </c>
       <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
         <v>53.51013691416535</v>
       </c>
     </row>
@@ -5297,15 +5671,18 @@
         <v>5.781990521327014</v>
       </c>
       <c r="H125" t="n">
-        <v>20</v>
+        <v>4.004739336492891</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
       </c>
       <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
         <v>53.33754607688257</v>
       </c>
     </row>
@@ -5336,15 +5713,18 @@
         <v>5.497630331753554</v>
       </c>
       <c r="H126" t="n">
-        <v>20</v>
+        <v>1.658767772511848</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
         <v>53.21985255397578</v>
       </c>
     </row>
@@ -5375,15 +5755,18 @@
         <v>3.222748815165877</v>
       </c>
       <c r="H127" t="n">
-        <v>20</v>
+        <v>3.270142180094787</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
       </c>
       <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
         <v>52.7763202437373</v>
       </c>
     </row>
@@ -5414,15 +5797,18 @@
         <v>4.739336492890995</v>
       </c>
       <c r="H128" t="n">
-        <v>20</v>
+        <v>4.881516587677725</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
       </c>
       <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
         <v>50.07266982622433</v>
       </c>
     </row>
@@ -5453,15 +5839,18 @@
         <v>5.876777251184834</v>
       </c>
       <c r="H129" t="n">
-        <v>20</v>
+        <v>4.5260663507109</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
       </c>
       <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
         <v>49.00177725118483</v>
       </c>
     </row>
@@ -5492,15 +5881,18 @@
         <v>1.516587677725119</v>
       </c>
       <c r="H130" t="n">
-        <v>20</v>
+        <v>3.625592417061612</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
       </c>
       <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
         <v>48.57015910629654</v>
       </c>
     </row>
@@ -5531,15 +5923,18 @@
         <v>9.004739336492891</v>
       </c>
       <c r="H131" t="n">
-        <v>20</v>
+        <v>2.251184834123223</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
       </c>
       <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
         <v>48.20116790792147</v>
       </c>
     </row>
@@ -5570,15 +5965,18 @@
         <v>12.70142180094787</v>
       </c>
       <c r="H132" t="n">
-        <v>20</v>
+        <v>4.76303317535545</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
       </c>
       <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
         <v>47.96927894380501</v>
       </c>
     </row>
@@ -5609,15 +6007,18 @@
         <v>13.45971563981043</v>
       </c>
       <c r="H133" t="n">
-        <v>20</v>
+        <v>1.066350710900474</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
       </c>
       <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
         <v>46.95971563981043</v>
       </c>
     </row>
@@ -5648,15 +6049,18 @@
         <v>6.255924170616113</v>
       </c>
       <c r="H134" t="n">
-        <v>20</v>
+        <v>0.4502369668246445</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
         <v>46.894813059505</v>
       </c>
     </row>
@@ -5687,15 +6091,18 @@
         <v>8.625592417061611</v>
       </c>
       <c r="H135" t="n">
-        <v>20</v>
+        <v>4.289099526066351</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
       </c>
       <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
         <v>46.83987813134733</v>
       </c>
     </row>
@@ -5726,15 +6133,18 @@
         <v>0.7582938388625593</v>
       </c>
       <c r="H136" t="n">
-        <v>20</v>
+        <v>0.1184834123222749</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
       </c>
       <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
         <v>46.48051606108478</v>
       </c>
     </row>
@@ -5765,15 +6175,18 @@
         <v>1.706161137440758</v>
       </c>
       <c r="H137" t="n">
-        <v>20</v>
+        <v>2.345971563981043</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
       </c>
       <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
         <v>46.08116113744076</v>
       </c>
     </row>
@@ -5804,15 +6217,18 @@
         <v>0.3791469194312796</v>
       </c>
       <c r="H138" t="n">
-        <v>20</v>
+        <v>3.009478672985782</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
       </c>
       <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
         <v>44.32359136387572</v>
       </c>
     </row>
@@ -5843,15 +6259,18 @@
         <v>9.099526066350711</v>
       </c>
       <c r="H139" t="n">
-        <v>20</v>
+        <v>2.654028436018958</v>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
       </c>
       <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
         <v>44.32174828857293</v>
       </c>
     </row>
@@ -5882,15 +6301,18 @@
         <v>2.274881516587678</v>
       </c>
       <c r="H140" t="n">
-        <v>20</v>
+        <v>0.7819905213270142</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
       </c>
       <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
         <v>44.05265929436545</v>
       </c>
     </row>
@@ -5921,15 +6343,18 @@
         <v>11.18483412322275</v>
       </c>
       <c r="H141" t="n">
-        <v>20</v>
+        <v>0.9715639810426541</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
       </c>
       <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
         <v>43.01816745655609</v>
       </c>
     </row>
@@ -5960,15 +6385,18 @@
         <v>4.265402843601896</v>
       </c>
       <c r="H142" t="n">
-        <v>20</v>
+        <v>0.947867298578199</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
       </c>
       <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
         <v>41.15429173249078</v>
       </c>
     </row>
@@ -5999,15 +6427,18 @@
         <v>2.464454976303317</v>
       </c>
       <c r="H143" t="n">
-        <v>20</v>
+        <v>3.838862559241706</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
       </c>
       <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
         <v>38.00016926201761</v>
       </c>
     </row>
@@ -6038,15 +6469,18 @@
         <v>0.6635071090047394</v>
       </c>
       <c r="H144" t="n">
-        <v>20</v>
+        <v>0.9952606635071091</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
         <v>37.85100710900474</v>
       </c>
     </row>
@@ -6077,15 +6511,18 @@
         <v>3.127962085308057</v>
       </c>
       <c r="H145" t="n">
-        <v>20</v>
+        <v>4.71563981042654</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
       <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
         <v>36.60018430753028</v>
       </c>
     </row>
@@ -6116,15 +6553,18 @@
         <v>2.748815165876777</v>
       </c>
       <c r="H146" t="n">
-        <v>20</v>
+        <v>3.364928909952607</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
       </c>
       <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
         <v>36.19325961032122</v>
       </c>
     </row>
@@ -6155,15 +6595,18 @@
         <v>1.895734597156398</v>
       </c>
       <c r="H147" t="n">
-        <v>20</v>
+        <v>3.720379146919432</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
       </c>
       <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
         <v>29.34017904160084</v>
       </c>
     </row>
@@ -6194,15 +6637,18 @@
         <v>19.71563981042654</v>
       </c>
       <c r="H148" t="n">
+        <v>3.104265402843602</v>
+      </c>
+      <c r="I148" t="n">
         <v>8</v>
       </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
         <v>27.71563981042654</v>
       </c>
     </row>
@@ -6233,15 +6679,18 @@
         <v>18.95734597156398</v>
       </c>
       <c r="H149" t="n">
+        <v>2.203791469194313</v>
+      </c>
+      <c r="I149" t="n">
         <v>8</v>
       </c>
-      <c r="I149" t="n">
-        <v>0</v>
-      </c>
       <c r="J149" t="n">
         <v>0</v>
       </c>
       <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
         <v>26.95734597156398</v>
       </c>
     </row>
@@ -6272,15 +6721,18 @@
         <v>18.86255924170616</v>
       </c>
       <c r="H150" t="n">
+        <v>2.772511848341232</v>
+      </c>
+      <c r="I150" t="n">
         <v>8</v>
       </c>
-      <c r="I150" t="n">
-        <v>0</v>
-      </c>
       <c r="J150" t="n">
         <v>0</v>
       </c>
       <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
         <v>26.86255924170616</v>
       </c>
     </row>
@@ -6311,15 +6763,18 @@
         <v>18.67298578199052</v>
       </c>
       <c r="H151" t="n">
+        <v>2.037914691943128</v>
+      </c>
+      <c r="I151" t="n">
         <v>8</v>
       </c>
-      <c r="I151" t="n">
-        <v>0</v>
-      </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
         <v>26.67298578199052</v>
       </c>
     </row>
@@ -6350,15 +6805,18 @@
         <v>18.48341232227488</v>
       </c>
       <c r="H152" t="n">
+        <v>0.3080568720379147</v>
+      </c>
+      <c r="I152" t="n">
         <v>8</v>
       </c>
-      <c r="I152" t="n">
-        <v>0</v>
-      </c>
       <c r="J152" t="n">
         <v>0</v>
       </c>
       <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
         <v>26.48341232227488</v>
       </c>
     </row>
@@ -6389,15 +6847,18 @@
         <v>18.29383886255924</v>
       </c>
       <c r="H153" t="n">
+        <v>2.985781990521327</v>
+      </c>
+      <c r="I153" t="n">
         <v>8</v>
       </c>
-      <c r="I153" t="n">
-        <v>0</v>
-      </c>
       <c r="J153" t="n">
         <v>0</v>
       </c>
       <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
         <v>26.29383886255924</v>
       </c>
     </row>
@@ -6428,15 +6889,18 @@
         <v>17.91469194312796</v>
       </c>
       <c r="H154" t="n">
+        <v>2.630331753554502</v>
+      </c>
+      <c r="I154" t="n">
         <v>8</v>
       </c>
-      <c r="I154" t="n">
-        <v>0</v>
-      </c>
       <c r="J154" t="n">
         <v>0</v>
       </c>
       <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
         <v>25.91469194312796</v>
       </c>
     </row>
@@ -6467,15 +6931,18 @@
         <v>17.6303317535545</v>
       </c>
       <c r="H155" t="n">
+        <v>1.279620853080569</v>
+      </c>
+      <c r="I155" t="n">
         <v>8</v>
       </c>
-      <c r="I155" t="n">
-        <v>0</v>
-      </c>
       <c r="J155" t="n">
         <v>0</v>
       </c>
       <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
         <v>25.6303317535545</v>
       </c>
     </row>
@@ -6506,15 +6973,18 @@
         <v>17.53554502369668</v>
       </c>
       <c r="H156" t="n">
+        <v>1.232227488151659</v>
+      </c>
+      <c r="I156" t="n">
         <v>8</v>
       </c>
-      <c r="I156" t="n">
-        <v>0</v>
-      </c>
       <c r="J156" t="n">
         <v>0</v>
       </c>
       <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
         <v>25.53554502369668</v>
       </c>
     </row>
@@ -6545,15 +7015,18 @@
         <v>17.06161137440758</v>
       </c>
       <c r="H157" t="n">
+        <v>3.459715639810427</v>
+      </c>
+      <c r="I157" t="n">
         <v>8</v>
       </c>
-      <c r="I157" t="n">
-        <v>0</v>
-      </c>
       <c r="J157" t="n">
         <v>0</v>
       </c>
       <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
         <v>25.06161137440758</v>
       </c>
     </row>
@@ -6584,15 +7057,18 @@
         <v>16.2085308056872</v>
       </c>
       <c r="H158" t="n">
+        <v>2.322274881516588</v>
+      </c>
+      <c r="I158" t="n">
         <v>8</v>
       </c>
-      <c r="I158" t="n">
-        <v>0</v>
-      </c>
       <c r="J158" t="n">
         <v>0</v>
       </c>
       <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
         <v>24.2085308056872</v>
       </c>
     </row>
@@ -6623,15 +7099,18 @@
         <v>16.11374407582938</v>
       </c>
       <c r="H159" t="n">
+        <v>3.127962085308057</v>
+      </c>
+      <c r="I159" t="n">
         <v>8</v>
       </c>
-      <c r="I159" t="n">
-        <v>0</v>
-      </c>
       <c r="J159" t="n">
         <v>0</v>
       </c>
       <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
         <v>24.11374407582938</v>
       </c>
     </row>
@@ -6662,15 +7141,18 @@
         <v>14.78672985781991</v>
       </c>
       <c r="H160" t="n">
+        <v>3.388625592417061</v>
+      </c>
+      <c r="I160" t="n">
         <v>8</v>
       </c>
-      <c r="I160" t="n">
-        <v>0</v>
-      </c>
       <c r="J160" t="n">
         <v>0</v>
       </c>
       <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
         <v>22.78672985781991</v>
       </c>
     </row>
@@ -6701,15 +7183,18 @@
         <v>14.69194312796209</v>
       </c>
       <c r="H161" t="n">
+        <v>0.1658767772511849</v>
+      </c>
+      <c r="I161" t="n">
         <v>8</v>
       </c>
-      <c r="I161" t="n">
-        <v>0</v>
-      </c>
       <c r="J161" t="n">
         <v>0</v>
       </c>
       <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
         <v>22.69194312796208</v>
       </c>
     </row>
@@ -6740,15 +7225,18 @@
         <v>13.93364928909953</v>
       </c>
       <c r="H162" t="n">
+        <v>1.824644549763033</v>
+      </c>
+      <c r="I162" t="n">
         <v>8</v>
       </c>
-      <c r="I162" t="n">
-        <v>0</v>
-      </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
         <v>21.93364928909953</v>
       </c>
     </row>
@@ -6779,15 +7267,18 @@
         <v>13.83886255924171</v>
       </c>
       <c r="H163" t="n">
+        <v>0.7582938388625593</v>
+      </c>
+      <c r="I163" t="n">
         <v>8</v>
       </c>
-      <c r="I163" t="n">
-        <v>0</v>
-      </c>
       <c r="J163" t="n">
         <v>0</v>
       </c>
       <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
         <v>21.83886255924171</v>
       </c>
     </row>
@@ -6818,15 +7309,18 @@
         <v>13.74407582938389</v>
       </c>
       <c r="H164" t="n">
+        <v>0.5924170616113744</v>
+      </c>
+      <c r="I164" t="n">
         <v>8</v>
       </c>
-      <c r="I164" t="n">
-        <v>0</v>
-      </c>
       <c r="J164" t="n">
         <v>0</v>
       </c>
       <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
         <v>21.74407582938389</v>
       </c>
     </row>
@@ -6857,15 +7351,18 @@
         <v>13.27014218009479</v>
       </c>
       <c r="H165" t="n">
+        <v>2.464454976303317</v>
+      </c>
+      <c r="I165" t="n">
         <v>8</v>
       </c>
-      <c r="I165" t="n">
-        <v>0</v>
-      </c>
       <c r="J165" t="n">
         <v>0</v>
       </c>
       <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
         <v>21.27014218009479</v>
       </c>
     </row>
@@ -6896,15 +7393,18 @@
         <v>12.98578199052133</v>
       </c>
       <c r="H166" t="n">
+        <v>0.8056872037914692</v>
+      </c>
+      <c r="I166" t="n">
         <v>8</v>
       </c>
-      <c r="I166" t="n">
-        <v>0</v>
-      </c>
       <c r="J166" t="n">
         <v>0</v>
       </c>
       <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
         <v>20.98578199052133</v>
       </c>
     </row>
@@ -6935,15 +7435,18 @@
         <v>12.41706161137441</v>
       </c>
       <c r="H167" t="n">
+        <v>1.753554502369668</v>
+      </c>
+      <c r="I167" t="n">
         <v>8</v>
       </c>
-      <c r="I167" t="n">
-        <v>0</v>
-      </c>
       <c r="J167" t="n">
         <v>0</v>
       </c>
       <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
         <v>20.41706161137441</v>
       </c>
     </row>
@@ -6974,15 +7477,18 @@
         <v>11.65876777251185</v>
       </c>
       <c r="H168" t="n">
+        <v>0.5450236966824644</v>
+      </c>
+      <c r="I168" t="n">
         <v>8</v>
       </c>
-      <c r="I168" t="n">
-        <v>0</v>
-      </c>
       <c r="J168" t="n">
         <v>0</v>
       </c>
       <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
         <v>19.65876777251185</v>
       </c>
     </row>
@@ -7013,15 +7519,18 @@
         <v>11.56398104265403</v>
       </c>
       <c r="H169" t="n">
+        <v>2.855450236966824</v>
+      </c>
+      <c r="I169" t="n">
         <v>8</v>
       </c>
-      <c r="I169" t="n">
-        <v>0</v>
-      </c>
       <c r="J169" t="n">
         <v>0</v>
       </c>
       <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
         <v>19.56398104265403</v>
       </c>
     </row>
@@ -7052,15 +7561,18 @@
         <v>10.99526066350711</v>
       </c>
       <c r="H170" t="n">
+        <v>0.1895734597156398</v>
+      </c>
+      <c r="I170" t="n">
         <v>8</v>
       </c>
-      <c r="I170" t="n">
-        <v>0</v>
-      </c>
       <c r="J170" t="n">
         <v>0</v>
       </c>
       <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
         <v>18.99526066350711</v>
       </c>
     </row>
@@ -7091,15 +7603,18 @@
         <v>10.80568720379147</v>
       </c>
       <c r="H171" t="n">
+        <v>4.360189573459715</v>
+      </c>
+      <c r="I171" t="n">
         <v>8</v>
       </c>
-      <c r="I171" t="n">
-        <v>0</v>
-      </c>
       <c r="J171" t="n">
         <v>0</v>
       </c>
       <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
         <v>18.80568720379147</v>
       </c>
     </row>
@@ -7130,15 +7645,18 @@
         <v>10.42654028436019</v>
       </c>
       <c r="H172" t="n">
+        <v>1.137440758293839</v>
+      </c>
+      <c r="I172" t="n">
         <v>8</v>
       </c>
-      <c r="I172" t="n">
-        <v>0</v>
-      </c>
       <c r="J172" t="n">
         <v>0</v>
       </c>
       <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
         <v>18.42654028436019</v>
       </c>
     </row>
@@ -7169,15 +7687,18 @@
         <v>9.383886255924171</v>
       </c>
       <c r="H173" t="n">
+        <v>1.208530805687204</v>
+      </c>
+      <c r="I173" t="n">
         <v>8</v>
       </c>
-      <c r="I173" t="n">
-        <v>0</v>
-      </c>
       <c r="J173" t="n">
         <v>0</v>
       </c>
       <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="n">
         <v>17.38388625592417</v>
       </c>
     </row>
@@ -7208,15 +7729,18 @@
         <v>8.436018957345972</v>
       </c>
       <c r="H174" t="n">
+        <v>1.327014218009479</v>
+      </c>
+      <c r="I174" t="n">
         <v>8</v>
       </c>
-      <c r="I174" t="n">
-        <v>0</v>
-      </c>
       <c r="J174" t="n">
         <v>0</v>
       </c>
       <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
         <v>16.43601895734597</v>
       </c>
     </row>
@@ -7247,15 +7771,18 @@
         <v>7.772511848341233</v>
       </c>
       <c r="H175" t="n">
+        <v>0.04739336492890996</v>
+      </c>
+      <c r="I175" t="n">
         <v>8</v>
       </c>
-      <c r="I175" t="n">
-        <v>0</v>
-      </c>
       <c r="J175" t="n">
         <v>0</v>
       </c>
       <c r="K175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" t="n">
         <v>15.77251184834123</v>
       </c>
     </row>
@@ -7286,15 +7813,18 @@
         <v>7.677725118483413</v>
       </c>
       <c r="H176" t="n">
+        <v>0.8767772511848342</v>
+      </c>
+      <c r="I176" t="n">
         <v>8</v>
       </c>
-      <c r="I176" t="n">
-        <v>0</v>
-      </c>
       <c r="J176" t="n">
         <v>0</v>
       </c>
       <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="n">
         <v>15.67772511848341</v>
       </c>
     </row>
@@ -7325,15 +7855,18 @@
         <v>7.582938388625592</v>
       </c>
       <c r="H177" t="n">
+        <v>2.393364928909953</v>
+      </c>
+      <c r="I177" t="n">
         <v>8</v>
       </c>
-      <c r="I177" t="n">
-        <v>0</v>
-      </c>
       <c r="J177" t="n">
         <v>0</v>
       </c>
       <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
         <v>15.58293838862559</v>
       </c>
     </row>
@@ -7364,15 +7897,18 @@
         <v>7.203791469194313</v>
       </c>
       <c r="H178" t="n">
+        <v>3.507109004739337</v>
+      </c>
+      <c r="I178" t="n">
         <v>8</v>
       </c>
-      <c r="I178" t="n">
-        <v>0</v>
-      </c>
       <c r="J178" t="n">
         <v>0</v>
       </c>
       <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
         <v>15.20379146919431</v>
       </c>
     </row>
@@ -7403,15 +7939,18 @@
         <v>7.109004739336493</v>
       </c>
       <c r="H179" t="n">
+        <v>3.554502369668247</v>
+      </c>
+      <c r="I179" t="n">
         <v>8</v>
       </c>
-      <c r="I179" t="n">
-        <v>0</v>
-      </c>
       <c r="J179" t="n">
         <v>0</v>
       </c>
       <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
         <v>15.10900473933649</v>
       </c>
     </row>
@@ -7442,15 +7981,18 @@
         <v>6.919431279620854</v>
       </c>
       <c r="H180" t="n">
+        <v>0.7109004739336493</v>
+      </c>
+      <c r="I180" t="n">
         <v>8</v>
       </c>
-      <c r="I180" t="n">
-        <v>0</v>
-      </c>
       <c r="J180" t="n">
         <v>0</v>
       </c>
       <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
         <v>14.91943127962085</v>
       </c>
     </row>
@@ -7481,15 +8023,18 @@
         <v>6.729857819905213</v>
       </c>
       <c r="H181" t="n">
+        <v>0.9241706161137441</v>
+      </c>
+      <c r="I181" t="n">
         <v>8</v>
       </c>
-      <c r="I181" t="n">
-        <v>0</v>
-      </c>
       <c r="J181" t="n">
         <v>0</v>
       </c>
       <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
         <v>14.72985781990521</v>
       </c>
     </row>
@@ -7520,15 +8065,18 @@
         <v>6.161137440758294</v>
       </c>
       <c r="H182" t="n">
+        <v>1.255924170616114</v>
+      </c>
+      <c r="I182" t="n">
         <v>8</v>
       </c>
-      <c r="I182" t="n">
-        <v>0</v>
-      </c>
       <c r="J182" t="n">
         <v>0</v>
       </c>
       <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
         <v>14.16113744075829</v>
       </c>
     </row>
@@ -7559,15 +8107,18 @@
         <v>5.687203791469194</v>
       </c>
       <c r="H183" t="n">
+        <v>4.099526066350711</v>
+      </c>
+      <c r="I183" t="n">
         <v>8</v>
       </c>
-      <c r="I183" t="n">
-        <v>0</v>
-      </c>
       <c r="J183" t="n">
         <v>0</v>
       </c>
       <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
         <v>13.68720379146919</v>
       </c>
     </row>
@@ -7598,15 +8149,18 @@
         <v>5.213270142180095</v>
       </c>
       <c r="H184" t="n">
+        <v>0.2132701421800948</v>
+      </c>
+      <c r="I184" t="n">
         <v>8</v>
       </c>
-      <c r="I184" t="n">
-        <v>0</v>
-      </c>
       <c r="J184" t="n">
         <v>0</v>
       </c>
       <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
         <v>13.21327014218009</v>
       </c>
     </row>
@@ -7637,15 +8191,18 @@
         <v>4.549763033175355</v>
       </c>
       <c r="H185" t="n">
+        <v>3.293838862559242</v>
+      </c>
+      <c r="I185" t="n">
         <v>8</v>
       </c>
-      <c r="I185" t="n">
-        <v>0</v>
-      </c>
       <c r="J185" t="n">
         <v>0</v>
       </c>
       <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
         <v>12.54976303317536</v>
       </c>
     </row>
@@ -7676,15 +8233,18 @@
         <v>4.454976303317536</v>
       </c>
       <c r="H186" t="n">
+        <v>1.090047393364929</v>
+      </c>
+      <c r="I186" t="n">
         <v>8</v>
       </c>
-      <c r="I186" t="n">
-        <v>0</v>
-      </c>
       <c r="J186" t="n">
         <v>0</v>
       </c>
       <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
         <v>12.45497630331754</v>
       </c>
     </row>
@@ -7715,15 +8275,18 @@
         <v>4.170616113744075</v>
       </c>
       <c r="H187" t="n">
+        <v>2.180094786729858</v>
+      </c>
+      <c r="I187" t="n">
         <v>8</v>
       </c>
-      <c r="I187" t="n">
-        <v>0</v>
-      </c>
       <c r="J187" t="n">
         <v>0</v>
       </c>
       <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
         <v>12.17061611374407</v>
       </c>
     </row>
@@ -7754,15 +8317,18 @@
         <v>4.075829383886256</v>
       </c>
       <c r="H188" t="n">
+        <v>3.199052132701421</v>
+      </c>
+      <c r="I188" t="n">
         <v>8</v>
       </c>
-      <c r="I188" t="n">
-        <v>0</v>
-      </c>
       <c r="J188" t="n">
         <v>0</v>
       </c>
       <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
         <v>12.07582938388625</v>
       </c>
     </row>
@@ -7793,15 +8359,18 @@
         <v>3.981042654028436</v>
       </c>
       <c r="H189" t="n">
+        <v>1.611374407582938</v>
+      </c>
+      <c r="I189" t="n">
         <v>8</v>
       </c>
-      <c r="I189" t="n">
-        <v>0</v>
-      </c>
       <c r="J189" t="n">
         <v>0</v>
       </c>
       <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
         <v>11.98104265402844</v>
       </c>
     </row>
@@ -7832,15 +8401,18 @@
         <v>3.696682464454976</v>
       </c>
       <c r="H190" t="n">
+        <v>2.417061611374407</v>
+      </c>
+      <c r="I190" t="n">
         <v>8</v>
       </c>
-      <c r="I190" t="n">
-        <v>0</v>
-      </c>
       <c r="J190" t="n">
         <v>0</v>
       </c>
       <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
         <v>11.69668246445498</v>
       </c>
     </row>
@@ -7871,15 +8443,18 @@
         <v>3.601895734597156</v>
       </c>
       <c r="H191" t="n">
+        <v>3.909952606635071</v>
+      </c>
+      <c r="I191" t="n">
         <v>8</v>
       </c>
-      <c r="I191" t="n">
-        <v>0</v>
-      </c>
       <c r="J191" t="n">
         <v>0</v>
       </c>
       <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="n">
         <v>11.60189573459716</v>
       </c>
     </row>
@@ -7910,15 +8485,18 @@
         <v>3.412322274881517</v>
       </c>
       <c r="H192" t="n">
+        <v>4.502369668246446</v>
+      </c>
+      <c r="I192" t="n">
         <v>8</v>
       </c>
-      <c r="I192" t="n">
-        <v>0</v>
-      </c>
       <c r="J192" t="n">
         <v>0</v>
       </c>
       <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
         <v>11.41232227488152</v>
       </c>
     </row>
@@ -7949,15 +8527,18 @@
         <v>3.033175355450237</v>
       </c>
       <c r="H193" t="n">
+        <v>0.4265402843601896</v>
+      </c>
+      <c r="I193" t="n">
         <v>8</v>
       </c>
-      <c r="I193" t="n">
-        <v>0</v>
-      </c>
       <c r="J193" t="n">
         <v>0</v>
       </c>
       <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
         <v>11.03317535545024</v>
       </c>
     </row>
@@ -7988,15 +8569,18 @@
         <v>2.938388625592417</v>
       </c>
       <c r="H194" t="n">
+        <v>0.09478672985781991</v>
+      </c>
+      <c r="I194" t="n">
         <v>8</v>
       </c>
-      <c r="I194" t="n">
-        <v>0</v>
-      </c>
       <c r="J194" t="n">
         <v>0</v>
       </c>
       <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
         <v>10.93838862559242</v>
       </c>
     </row>
@@ -8027,15 +8611,18 @@
         <v>2.843601895734597</v>
       </c>
       <c r="H195" t="n">
+        <v>4.38388625592417</v>
+      </c>
+      <c r="I195" t="n">
         <v>8</v>
       </c>
-      <c r="I195" t="n">
-        <v>0</v>
-      </c>
       <c r="J195" t="n">
         <v>0</v>
       </c>
       <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
         <v>10.8436018957346</v>
       </c>
     </row>
@@ -8066,15 +8653,18 @@
         <v>2.654028436018958</v>
       </c>
       <c r="H196" t="n">
+        <v>4.478672985781991</v>
+      </c>
+      <c r="I196" t="n">
         <v>8</v>
       </c>
-      <c r="I196" t="n">
-        <v>0</v>
-      </c>
       <c r="J196" t="n">
         <v>0</v>
       </c>
       <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
         <v>10.65402843601896</v>
       </c>
     </row>
@@ -8105,15 +8695,18 @@
         <v>2.559241706161137</v>
       </c>
       <c r="H197" t="n">
+        <v>1.540284360189573</v>
+      </c>
+      <c r="I197" t="n">
         <v>8</v>
       </c>
-      <c r="I197" t="n">
-        <v>0</v>
-      </c>
       <c r="J197" t="n">
         <v>0</v>
       </c>
       <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
         <v>10.55924170616114</v>
       </c>
     </row>
@@ -8144,15 +8737,18 @@
         <v>2.369668246445498</v>
       </c>
       <c r="H198" t="n">
+        <v>1.018957345971564</v>
+      </c>
+      <c r="I198" t="n">
         <v>8</v>
       </c>
-      <c r="I198" t="n">
-        <v>0</v>
-      </c>
       <c r="J198" t="n">
         <v>0</v>
       </c>
       <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
         <v>10.3696682464455</v>
       </c>
     </row>
@@ -8183,15 +8779,18 @@
         <v>2.180094786729858</v>
       </c>
       <c r="H199" t="n">
+        <v>1.042654028436019</v>
+      </c>
+      <c r="I199" t="n">
         <v>8</v>
       </c>
-      <c r="I199" t="n">
-        <v>0</v>
-      </c>
       <c r="J199" t="n">
         <v>0</v>
       </c>
       <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
         <v>10.18009478672986</v>
       </c>
     </row>
@@ -8222,15 +8821,18 @@
         <v>1.990521327014218</v>
       </c>
       <c r="H200" t="n">
+        <v>0.6872037914691943</v>
+      </c>
+      <c r="I200" t="n">
         <v>8</v>
       </c>
-      <c r="I200" t="n">
-        <v>0</v>
-      </c>
       <c r="J200" t="n">
         <v>0</v>
       </c>
       <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
         <v>9.990521327014218</v>
       </c>
     </row>
@@ -8261,15 +8863,18 @@
         <v>1.800947867298578</v>
       </c>
       <c r="H201" t="n">
+        <v>2.582938388625593</v>
+      </c>
+      <c r="I201" t="n">
         <v>8</v>
       </c>
-      <c r="I201" t="n">
-        <v>0</v>
-      </c>
       <c r="J201" t="n">
         <v>0</v>
       </c>
       <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
         <v>9.800947867298579</v>
       </c>
     </row>
@@ -8300,15 +8905,18 @@
         <v>1.327014218009479</v>
       </c>
       <c r="H202" t="n">
+        <v>0.5213270142180094</v>
+      </c>
+      <c r="I202" t="n">
         <v>8</v>
       </c>
-      <c r="I202" t="n">
-        <v>0</v>
-      </c>
       <c r="J202" t="n">
         <v>0</v>
       </c>
       <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
         <v>9.327014218009479</v>
       </c>
     </row>
@@ -8339,15 +8947,18 @@
         <v>1.232227488151659</v>
       </c>
       <c r="H203" t="n">
+        <v>1.635071090047393</v>
+      </c>
+      <c r="I203" t="n">
         <v>8</v>
       </c>
-      <c r="I203" t="n">
-        <v>0</v>
-      </c>
       <c r="J203" t="n">
         <v>0</v>
       </c>
       <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
         <v>9.232227488151658</v>
       </c>
     </row>
@@ -8378,15 +8989,18 @@
         <v>1.137440758293839</v>
       </c>
       <c r="H204" t="n">
+        <v>0.2843601895734597</v>
+      </c>
+      <c r="I204" t="n">
         <v>8</v>
       </c>
-      <c r="I204" t="n">
-        <v>0</v>
-      </c>
       <c r="J204" t="n">
         <v>0</v>
       </c>
       <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
         <v>9.137440758293838</v>
       </c>
     </row>
@@ -8417,15 +9031,18 @@
         <v>1.042654028436019</v>
       </c>
       <c r="H205" t="n">
+        <v>0.4739336492890995</v>
+      </c>
+      <c r="I205" t="n">
         <v>8</v>
       </c>
-      <c r="I205" t="n">
-        <v>0</v>
-      </c>
       <c r="J205" t="n">
         <v>0</v>
       </c>
       <c r="K205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" t="n">
         <v>9.042654028436019</v>
       </c>
     </row>
@@ -8456,15 +9073,18 @@
         <v>0.947867298578199</v>
       </c>
       <c r="H206" t="n">
+        <v>3.957345971563981</v>
+      </c>
+      <c r="I206" t="n">
         <v>8</v>
       </c>
-      <c r="I206" t="n">
-        <v>0</v>
-      </c>
       <c r="J206" t="n">
         <v>0</v>
       </c>
       <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
         <v>8.947867298578199</v>
       </c>
     </row>
@@ -8495,15 +9115,18 @@
         <v>0.8530805687203792</v>
       </c>
       <c r="H207" t="n">
+        <v>1.469194312796208</v>
+      </c>
+      <c r="I207" t="n">
         <v>8</v>
       </c>
-      <c r="I207" t="n">
-        <v>0</v>
-      </c>
       <c r="J207" t="n">
         <v>0</v>
       </c>
       <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
         <v>8.85308056872038</v>
       </c>
     </row>
@@ -8534,15 +9157,18 @@
         <v>0.5687203791469194</v>
       </c>
       <c r="H208" t="n">
+        <v>0.07109004739336493</v>
+      </c>
+      <c r="I208" t="n">
         <v>8</v>
       </c>
-      <c r="I208" t="n">
-        <v>0</v>
-      </c>
       <c r="J208" t="n">
         <v>0</v>
       </c>
       <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
         <v>8.568720379146919</v>
       </c>
     </row>
@@ -8573,15 +9199,18 @@
         <v>0.4739336492890995</v>
       </c>
       <c r="H209" t="n">
+        <v>0.8530805687203792</v>
+      </c>
+      <c r="I209" t="n">
         <v>8</v>
       </c>
-      <c r="I209" t="n">
-        <v>0</v>
-      </c>
       <c r="J209" t="n">
         <v>0</v>
       </c>
       <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
         <v>8.4739336492891</v>
       </c>
     </row>
@@ -8612,15 +9241,18 @@
         <v>0.2843601895734597</v>
       </c>
       <c r="H210" t="n">
+        <v>2.227488151658768</v>
+      </c>
+      <c r="I210" t="n">
         <v>8</v>
       </c>
-      <c r="I210" t="n">
-        <v>0</v>
-      </c>
       <c r="J210" t="n">
         <v>0</v>
       </c>
       <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
         <v>8.28436018957346</v>
       </c>
     </row>
@@ -8651,15 +9283,18 @@
         <v>0.1895734597156398</v>
       </c>
       <c r="H211" t="n">
+        <v>0.7345971563981042</v>
+      </c>
+      <c r="I211" t="n">
         <v>8</v>
       </c>
-      <c r="I211" t="n">
-        <v>0</v>
-      </c>
       <c r="J211" t="n">
         <v>0</v>
       </c>
       <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
         <v>8.189573459715639</v>
       </c>
     </row>
@@ -8690,15 +9325,18 @@
         <v>0.09478672985781991</v>
       </c>
       <c r="H212" t="n">
+        <v>2.914691943127962</v>
+      </c>
+      <c r="I212" t="n">
         <v>8</v>
       </c>
-      <c r="I212" t="n">
-        <v>0</v>
-      </c>
       <c r="J212" t="n">
         <v>0</v>
       </c>
       <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
         <v>8.09478672985782</v>
       </c>
     </row>
